--- a/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="49281" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="51298" uniqueCount="782">
   <si>
     <t>Year</t>
   </si>
@@ -1691,6 +1691,675 @@
   </si>
   <si>
     <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040517\fracture\Fracture_20230405_170828_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_033016\compression\COMPRESSION_20230417_163903_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_033016\compression\COMPRESSION_20230417_163903_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_033016\tension\TENSION_20230417_165352_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_033016\tension\TENSION_20230417_165352_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_033016\fracture\Fracture_20230417_162808_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_033016\fracture\Fracture_20230417_162808_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_033016\fracture\Fracture_20230417_161539_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_033016\fracture\Fracture_20230417_161539_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_033016\fracture\Fracture_20230417_162808_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_033016\fracture\Fracture_20230417_162808_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_033016\fracture\Fracture_20230417_161539_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_033016\fracture\Fracture_20230417_161539_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040308\fracture\Fracture_20230403_90454_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040308\fracture\Fracture_20230403_90454_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040308\fracture\Fracture_20230403_92519_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040308\fracture\Fracture_20230403_90454_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040308\fracture\Fracture_20230403_90454_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040308\fracture\Fracture_20230403_92519_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040308\fracture\Fracture_20230403_92519_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040308\fracture\Fracture_20230403_92519_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040309\fracture\Fracture_20230417_95939_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040309\fracture\Fracture_20230417_95939_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040309\fracture\Fracture_20230417_95939_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040309\fracture\Fracture_20230417_95254_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040309\fracture\Fracture_20230417_95939_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040309\fracture\Fracture_20230417_95254_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040309\fracture\Fracture_20230417_95254_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040309\fracture\Fracture_20230417_95254_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040316\compression\COMPRESSION_20230403_163602_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040316\compression\COMPRESSION_20230403_163602_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040316\fracture\Fracture_20230403_153304_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040316\fracture\Fracture_20230403_153304_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040316\fracture\Fracture_20230403_153304_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040316\fracture\Fracture_20230403_153304_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040316\fracture\Fracture_20230403_161101_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040316\fracture\Fracture_20230403_161101_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040316\fracture\Fracture_20230403_161101_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040316\fracture\Fracture_20230403_161101_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040308\fracture\Fracture_20230404_83342_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040308\fracture\Fracture_20230404_85357_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040308\fracture\Fracture_20230404_83342_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040308\fracture\Fracture_20230404_85357_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040308\fracture\Fracture_20230404_83342_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040308\fracture\Fracture_20230404_83342_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040308\fracture\Fracture_20230404_85357_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040308\fracture\Fracture_20230404_85357_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040411\compression\COMPRESSION_20230404_115233_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040411\compression\COMPRESSION_20230404_114857_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040411\tension\TENSION_20230404_111738_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040411\tension\TENSION_20230404_113913_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040411\fracture\Fracture_20230404_121630_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040411\fracture\Fracture_20230404_121630_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040411\fracture\Fracture_20230404_121630_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040411\fracture\Fracture_20230404_121630_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040414\fracture\Fracture_20230404_143714_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040414\fracture\Fracture_20230404_143714_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040414\fracture\Fracture_20230404_143714_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040414\fracture\Fracture_20230404_143714_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040416\compression\COMPRESSION_20231114_160620_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040416\compression\COMPRESSION_20231114_160620_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040416\tension\TENSION_20231114_155317_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040416\tension\TENSION_20231114_155317_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040416\fracture\Fracture_20231114_165619_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040416\fracture\Fracture_20231114_165619_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040416\fracture\Fracture_20231114_164643_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040416\fracture\Fracture_20231114_165619_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040416\fracture\Fracture_20231114_165619_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040416\fracture\Fracture_20231114_164643_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040416\fracture\Fracture_20231114_164643_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040416\fracture\Fracture_20231114_164643_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040417\fracture\Fracture_20230404_180755_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040417\fracture\Fracture_20230404_180755_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040417\fracture\Fracture_20230404_180755_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040417\fracture\Fracture_20230404_175426_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040417\fracture\Fracture_20230404_175426_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040417\fracture\Fracture_20230403_90454_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040417\fracture\Fracture_20230404_175426_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040417\fracture\Fracture_20230404_175426_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040508\compression\COMPRESSION_20230405_91656_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040508\compression\COMPRESSION_20230405_91423_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040508\fracture\Fracture_20230405_85157_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040508\fracture\Fracture_20230405_85748_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040508\fracture\Fracture_20230405_85748_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040508\fracture\Fracture_20230405_85157_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040508\fracture\Fracture_20230405_85157_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040508\fracture\Fracture_20230405_85748_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040508\fracture\Fracture_20230405_85748_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040514\tension\TENSION_20230405_140132_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040514\tension\TENSION_20230405_140132_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040514\fracture\Fracture_20230405_142401_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040514\fracture\Fracture_20230405_142401_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040514\fracture\Fracture_20230405_142401_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040514\fracture\Fracture_20230403_92519_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040517\compression\COMPRESSION_20230405_171714_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040517\compression\COMPRESSION_20230405_171714_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040517\tension\TENSION_20230405_173912_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040517\tension\TENSION_20230405_173912_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040517\fracture\Fracture_20230405_164927_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040517\fracture\Fracture_20230405_164927_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040517\fracture\Fracture_20230405_164927_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040517\fracture\Fracture_20230405_170828_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040517\fracture\Fracture_20230405_170828_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040517\fracture\Fracture_20230405_164927_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040517\fracture\Fracture_20230405_170828_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040517\fracture\Fracture_20230405_170828_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040608\compression\COMPRESSION_20230406_93115_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040608\compression\COMPRESSION_20230406_93115_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040608\fracture\Fracture_20230406_92408_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040608\fracture\Fracture_20230406_85917_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040608\fracture\Fracture_20230406_85917_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040608\fracture\Fracture_20230406_85917_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040608\fracture\Fracture_20230406_92408_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040608\fracture\Fracture_20230406_92408_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040608\fracture\Fracture_20230406_85917_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040608\fracture\Fracture_20230406_92408_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040611\compression\COMPRESSION_20230406_112959_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040611\compression\COMPRESSION_20230406_112959_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040611\tension\TENSION_20230406_121949_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040611\fracture\Fracture_20230406_114350_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040611\fracture\Fracture_20230406_114350_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040611\fracture\Fracture_20230406_114350_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040611\fracture\Fracture_20230406_114350_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040611\fracture\Fracture_20230406_114350_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040611\fracture\Fracture_20230406_114350_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040611\fracture\Fracture_20230406_114350_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040611\fracture\Fracture_20230406_114350_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040614\compression\COMPRESSION_20230406_142547_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040614\compression\COMPRESSION_20230406_142547_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040614\tension\TENSION_20230406_141717_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040614\tension\TENSION_20230406_141717_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040614\fracture\Fracture_20230406_145409_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040614\fracture\Fracture_20230406_145409_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040614\fracture\Fracture_20230406_145409_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040614\fracture\Fracture_20230406_145409_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040614\fracture\Fracture_20230406_150045_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040614\fracture\Fracture_20230406_150045_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040614\fracture\Fracture_20230406_150045_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040614\fracture\Fracture_20230406_150045_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040618\compression\COMPRESSION_20230406_174442_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040618\tension\TENSION_20230406_180231_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040618\tension\TENSION_20230406_180231_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040618\fracture\Fracture_20230406_171011_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040618\fracture\Fracture_20230406_171011_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040618\fracture\Fracture_20230406_173843_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040618\fracture\Fracture_20230406_173843_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040618\fracture\Fracture_20230406_171011_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040618\fracture\Fracture_20230406_173843_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040618\fracture\Fracture_20230406_171011_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040618\fracture\Fracture_20230406_173843_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040414\compression\COMPRESSION_20230419_171957_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040414\compression\COMPRESSION_20230419_171957_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040414\tension\TENSION_20230419_173120_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040414\tension\TENSION_20230419_173120_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040414\fracture\Fracture_20230419_170432_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040414\fracture\Fracture_20230419_170432_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040414\fracture\Fracture_20230419_170432_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040414\fracture\Fracture_20230419_170432_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040414\fracture\Fracture_20230419_170432_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040414\fracture\Fracture_20230419_170432_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040414\fracture\Fracture_20230419_170432_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040708\compression\COMPRESSION_20230407_90153_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040708\compression\COMPRESSION_20230407_90153_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040708\tension\TENSION_20230407_84343_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040708\tension\TENSION_20230407_84343_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040708\fracture\Fracture_20230407_93404_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040708\fracture\Fracture_20230407_91721_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040708\fracture\Fracture_20230407_91721_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040708\fracture\Fracture_20230407_91721_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040708\fracture\Fracture_20230407_93404_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040708\fracture\Fracture_20230407_93404_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040708\fracture\Fracture_20230407_91721_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040708\fracture\Fracture_20230407_93404_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040714\compression\COMPRESSION_20230407_151551_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040714\compression\COMPRESSION_20230407_151551_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040714\tension\TENSION_20230407_145506_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040714\tension\TENSION_20230407_145506_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040714\fracture\Fracture_20230407_160903_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040714\fracture\Fracture_20230407_160903_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040714\fracture\Fracture_20230407_160903_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040714\fracture\Fracture_20230407_160903_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040714\fracture\Fracture_20230407_160903_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040714\fracture\Fracture_20230407_160903_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040714\fracture\Fracture_20230407_160903_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042109\tension\TENSION_20230421_92743_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042109\tension\TENSION_20230421_92743_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042109\fracture\Fracture_20230421_85231_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042109\fracture\Fracture_20230421_85231_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042109\fracture\Fracture_20230421_85231_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042109\fracture\Fracture_20230421_85231_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042109\fracture\Fracture_20230421_85231_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042109\fracture\Fracture_20230421_85231_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042109\fracture\Fracture_20230421_85231_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042111\compression\COMPRESSION_20230407_121438_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042111\compression\COMPRESSION_20230407_121438_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042111\tension\TENSION_20230407_123028_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042111\tension\TENSION_20230407_123028_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042111\fracture\Fracture_20230407_113420_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042111\fracture\Fracture_20230407_113420_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042111\fracture\Fracture_20230407_113420_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042111\fracture\Fracture_20230407_113420_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042111\fracture\Fracture_20230407_113420_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042111\fracture\Fracture_20230407_113420_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042111\fracture\Fracture_20230407_113420_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042111\fracture\Fracture_20230407_113420_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042115\compression\COMPRESSION_20230421_150517_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042115\compression\COMPRESSION_20230421_150517_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042115\tension\TENSION_20230421_144807_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042115\tension\TENSION_20230421_144807_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042115\fracture\Fracture_20230421_151658_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042115\fracture\Fracture_20230421_151658_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042115\fracture\Fracture_20230421_151658_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042115\fracture\Fracture_20230421_151658_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042115\fracture\Fracture_20230421_151658_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042115\fracture\Fracture_20230421_151658_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042115\fracture\Fracture_20230421_151658_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch2\wednesday\wednesday_111518\compression\COMPRESSION_20231115_193121_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch2\wednesday\wednesday_111518\compression\COMPRESSION_20231115_193121_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch2\wednesday\wednesday_111518\tension\TENSION_20231115_200051_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch2\wednesday\wednesday_111518\tension\TENSION_20231115_200051_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch2\wednesday\wednesday_111518\fracture\Fracture_20231115_190926_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch2\wednesday\wednesday_111518\fracture\Fracture_20231115_190926_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch2\wednesday\wednesday_111518\fracture\Fracture_20231115_185304_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch2\wednesday\wednesday_111518\fracture\Fracture_20231115_185304_3_2.csv</t>
   </si>
 </sst>
 </file>
@@ -1739,16 +2408,16 @@
   <dimension ref="A1:J238"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.08984375" customWidth="true"/>
-    <col min="2" max="2" width="6.54296875" customWidth="true"/>
-    <col min="3" max="3" width="10.36328125" customWidth="true"/>
-    <col min="4" max="4" width="17.36328125" customWidth="true"/>
-    <col min="5" max="5" width="11.81640625" customWidth="true"/>
-    <col min="6" max="6" width="11.90625" customWidth="true"/>
-    <col min="7" max="7" width="7.90625" customWidth="true"/>
-    <col min="8" max="8" width="36.26953125" customWidth="true"/>
-    <col min="9" max="9" width="168.54296875" customWidth="true"/>
-    <col min="10" max="10" width="10.453125" customWidth="true"/>
+    <col min="1" max="1" width="14.85546875" customWidth="true"/>
+    <col min="2" max="2" width="7" customWidth="true"/>
+    <col min="3" max="3" width="11.28515625" customWidth="true"/>
+    <col min="4" max="4" width="18.28515625" customWidth="true"/>
+    <col min="5" max="5" width="12.7109375" customWidth="true"/>
+    <col min="6" max="6" width="13" customWidth="true"/>
+    <col min="7" max="7" width="8.5703125" customWidth="true"/>
+    <col min="8" max="8" width="37.42578125" customWidth="true"/>
+    <col min="9" max="9" width="148" customWidth="true"/>
+    <col min="10" max="10" width="10.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1809,7 +2478,7 @@
         <v>46</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>241</v>
+        <v>559</v>
       </c>
       <c r="J2" s="0">
         <v>9347.0458999999992</v>
@@ -1841,7 +2510,7 @@
         <v>47</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>242</v>
+        <v>560</v>
       </c>
       <c r="J3" s="0">
         <v>9278.2314000000006</v>
@@ -1873,7 +2542,7 @@
         <v>48</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>243</v>
+        <v>561</v>
       </c>
       <c r="J4" s="0">
         <v>1582.4756</v>
@@ -1905,7 +2574,7 @@
         <v>49</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>244</v>
+        <v>562</v>
       </c>
       <c r="J5" s="0">
         <v>1241.5624</v>
@@ -1937,7 +2606,7 @@
         <v>50</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>245</v>
+        <v>563</v>
       </c>
       <c r="J6" s="0">
         <v>421.89870000000002</v>
@@ -1969,7 +2638,7 @@
         <v>51</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>246</v>
+        <v>564</v>
       </c>
       <c r="J7" s="0">
         <v>398.66129999999998</v>
@@ -2001,7 +2670,7 @@
         <v>52</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>247</v>
+        <v>565</v>
       </c>
       <c r="J8" s="0">
         <v>328.8254</v>
@@ -2033,7 +2702,7 @@
         <v>53</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>248</v>
+        <v>566</v>
       </c>
       <c r="J9" s="0">
         <v>313.2783</v>
@@ -2065,7 +2734,7 @@
         <v>54</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>249</v>
+        <v>567</v>
       </c>
       <c r="J10" s="0">
         <v>295.0641</v>
@@ -2097,7 +2766,7 @@
         <v>55</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>250</v>
+        <v>568</v>
       </c>
       <c r="J11" s="0">
         <v>294.86309999999998</v>
@@ -2129,7 +2798,7 @@
         <v>56</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>251</v>
+        <v>569</v>
       </c>
       <c r="J12" s="0">
         <v>281.74770000000001</v>
@@ -2161,7 +2830,7 @@
         <v>57</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>252</v>
+        <v>570</v>
       </c>
       <c r="J13" s="0">
         <v>274.15789999999998</v>
@@ -2193,7 +2862,7 @@
         <v>58</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>253</v>
+        <v>571</v>
       </c>
       <c r="J14" s="0">
         <v>370.1397</v>
@@ -2225,7 +2894,7 @@
         <v>59</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>254</v>
+        <v>572</v>
       </c>
       <c r="J15" s="0">
         <v>292.09550000000002</v>
@@ -2257,7 +2926,7 @@
         <v>60</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>255</v>
+        <v>573</v>
       </c>
       <c r="J16" s="0">
         <v>289.81389999999999</v>
@@ -2289,7 +2958,7 @@
         <v>61</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>256</v>
+        <v>574</v>
       </c>
       <c r="J17" s="0">
         <v>284.25450000000001</v>
@@ -2321,7 +2990,7 @@
         <v>62</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>257</v>
+        <v>575</v>
       </c>
       <c r="J18" s="0">
         <v>242.2781</v>
@@ -2353,7 +3022,7 @@
         <v>63</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>258</v>
+        <v>576</v>
       </c>
       <c r="J19" s="0">
         <v>223.45169999999999</v>
@@ -2385,7 +3054,7 @@
         <v>64</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>259</v>
+        <v>577</v>
       </c>
       <c r="J20" s="0">
         <v>199.1625</v>
@@ -2417,7 +3086,7 @@
         <v>65</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>260</v>
+        <v>578</v>
       </c>
       <c r="J21" s="0">
         <v>194.94929999999999</v>
@@ -2449,7 +3118,7 @@
         <v>66</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>261</v>
+        <v>579</v>
       </c>
       <c r="J22" s="0">
         <v>347.25940000000003</v>
@@ -2481,7 +3150,7 @@
         <v>67</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>262</v>
+        <v>580</v>
       </c>
       <c r="J23" s="0">
         <v>331.1694</v>
@@ -2513,7 +3182,7 @@
         <v>68</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>263</v>
+        <v>581</v>
       </c>
       <c r="J24" s="0">
         <v>321.93639999999999</v>
@@ -2545,7 +3214,7 @@
         <v>69</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>264</v>
+        <v>582</v>
       </c>
       <c r="J25" s="0">
         <v>277.89530000000002</v>
@@ -2577,7 +3246,7 @@
         <v>70</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>265</v>
+        <v>583</v>
       </c>
       <c r="J26" s="0">
         <v>276.74470000000002</v>
@@ -2609,7 +3278,7 @@
         <v>71</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>266</v>
+        <v>584</v>
       </c>
       <c r="J27" s="0">
         <v>268.73340000000002</v>
@@ -2641,7 +3310,7 @@
         <v>72</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>267</v>
+        <v>585</v>
       </c>
       <c r="J28" s="0">
         <v>267.4108</v>
@@ -2673,7 +3342,7 @@
         <v>73</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>268</v>
+        <v>586</v>
       </c>
       <c r="J29" s="0">
         <v>246.4597</v>
@@ -2705,7 +3374,7 @@
         <v>74</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>269</v>
+        <v>587</v>
       </c>
       <c r="J30" s="0">
         <v>9973.1728999999996</v>
@@ -2737,7 +3406,7 @@
         <v>75</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>270</v>
+        <v>588</v>
       </c>
       <c r="J31" s="0">
         <v>8216.1016</v>
@@ -2769,7 +3438,7 @@
         <v>76</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>271</v>
+        <v>589</v>
       </c>
       <c r="J32" s="0">
         <v>381.02080000000001</v>
@@ -2801,7 +3470,7 @@
         <v>77</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>272</v>
+        <v>590</v>
       </c>
       <c r="J33" s="0">
         <v>329.35809999999998</v>
@@ -2833,7 +3502,7 @@
         <v>78</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>273</v>
+        <v>591</v>
       </c>
       <c r="J34" s="0">
         <v>298.96679999999998</v>
@@ -2865,7 +3534,7 @@
         <v>79</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>274</v>
+        <v>592</v>
       </c>
       <c r="J35" s="0">
         <v>290.85469999999998</v>
@@ -2897,7 +3566,7 @@
         <v>80</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>275</v>
+        <v>593</v>
       </c>
       <c r="J36" s="0">
         <v>260.34840000000003</v>
@@ -2929,7 +3598,7 @@
         <v>81</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>276</v>
+        <v>594</v>
       </c>
       <c r="J37" s="0">
         <v>243.72470000000001</v>
@@ -2961,7 +3630,7 @@
         <v>82</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>277</v>
+        <v>595</v>
       </c>
       <c r="J38" s="0">
         <v>221.1927</v>
@@ -2993,7 +3662,7 @@
         <v>83</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>278</v>
+        <v>596</v>
       </c>
       <c r="J39" s="0">
         <v>210.51859999999999</v>
@@ -3025,7 +3694,7 @@
         <v>84</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>279</v>
+        <v>597</v>
       </c>
       <c r="J40" s="0">
         <v>368.1456</v>
@@ -3057,7 +3726,7 @@
         <v>85</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>280</v>
+        <v>598</v>
       </c>
       <c r="J41" s="0">
         <v>327.98309999999998</v>
@@ -3089,7 +3758,7 @@
         <v>86</v>
       </c>
       <c r="I42" s="0" t="s">
-        <v>281</v>
+        <v>599</v>
       </c>
       <c r="J42" s="0">
         <v>320.38529999999997</v>
@@ -3121,7 +3790,7 @@
         <v>87</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>282</v>
+        <v>600</v>
       </c>
       <c r="J43" s="0">
         <v>302.7507</v>
@@ -3153,7 +3822,7 @@
         <v>88</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>283</v>
+        <v>601</v>
       </c>
       <c r="J44" s="0">
         <v>278.7724</v>
@@ -3185,7 +3854,7 @@
         <v>89</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>284</v>
+        <v>602</v>
       </c>
       <c r="J45" s="0">
         <v>275.02319999999997</v>
@@ -3217,7 +3886,7 @@
         <v>90</v>
       </c>
       <c r="I46" s="0" t="s">
-        <v>285</v>
+        <v>603</v>
       </c>
       <c r="J46" s="0">
         <v>235.43600000000001</v>
@@ -3249,7 +3918,7 @@
         <v>91</v>
       </c>
       <c r="I47" s="0" t="s">
-        <v>286</v>
+        <v>604</v>
       </c>
       <c r="J47" s="0">
         <v>200.92150000000001</v>
@@ -3281,7 +3950,7 @@
         <v>92</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>287</v>
+        <v>605</v>
       </c>
       <c r="J48" s="0">
         <v>9411.1659999999993</v>
@@ -3313,7 +3982,7 @@
         <v>93</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>288</v>
+        <v>606</v>
       </c>
       <c r="J49" s="0">
         <v>9342.8192999999992</v>
@@ -3345,7 +4014,7 @@
         <v>94</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>289</v>
+        <v>607</v>
       </c>
       <c r="J50" s="0">
         <v>941.59280000000001</v>
@@ -3377,7 +4046,7 @@
         <v>95</v>
       </c>
       <c r="I51" s="0" t="s">
-        <v>290</v>
+        <v>608</v>
       </c>
       <c r="J51" s="0">
         <v>927.30880000000002</v>
@@ -3409,7 +4078,7 @@
         <v>96</v>
       </c>
       <c r="I52" s="0" t="s">
-        <v>291</v>
+        <v>609</v>
       </c>
       <c r="J52" s="0">
         <v>385.38529999999997</v>
@@ -3441,7 +4110,7 @@
         <v>97</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>292</v>
+        <v>610</v>
       </c>
       <c r="J53" s="0">
         <v>329.19709999999998</v>
@@ -3473,7 +4142,7 @@
         <v>98</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>293</v>
+        <v>611</v>
       </c>
       <c r="J54" s="0">
         <v>234.09270000000001</v>
@@ -3505,7 +4174,7 @@
         <v>99</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>294</v>
+        <v>612</v>
       </c>
       <c r="J55" s="0">
         <v>208.97069999999999</v>
@@ -3537,7 +4206,7 @@
         <v>100</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>295</v>
+        <v>613</v>
       </c>
       <c r="J56" s="0">
         <v>306.70839999999998</v>
@@ -3569,7 +4238,7 @@
         <v>101</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>296</v>
+        <v>614</v>
       </c>
       <c r="J57" s="0">
         <v>296.32659999999999</v>
@@ -3601,7 +4270,7 @@
         <v>102</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>297</v>
+        <v>615</v>
       </c>
       <c r="J58" s="0">
         <v>294.18619999999999</v>
@@ -3633,7 +4302,7 @@
         <v>103</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>298</v>
+        <v>616</v>
       </c>
       <c r="J59" s="0">
         <v>293.80200000000002</v>
@@ -3665,7 +4334,7 @@
         <v>104</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>299</v>
+        <v>617</v>
       </c>
       <c r="J60" s="0">
         <v>15461.819299999999</v>
@@ -3697,7 +4366,7 @@
         <v>105</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>300</v>
+        <v>618</v>
       </c>
       <c r="J61" s="0">
         <v>10367.752</v>
@@ -3729,7 +4398,7 @@
         <v>106</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>301</v>
+        <v>619</v>
       </c>
       <c r="J62" s="0">
         <v>1905.2927</v>
@@ -3761,7 +4430,7 @@
         <v>107</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>302</v>
+        <v>620</v>
       </c>
       <c r="J63" s="0">
         <v>975.92460000000005</v>
@@ -3793,7 +4462,7 @@
         <v>108</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>303</v>
+        <v>621</v>
       </c>
       <c r="J64" s="0">
         <v>581.38819999999998</v>
@@ -3825,7 +4494,7 @@
         <v>109</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>304</v>
+        <v>622</v>
       </c>
       <c r="J65" s="0">
         <v>546.27200000000005</v>
@@ -3857,7 +4526,7 @@
         <v>110</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>305</v>
+        <v>623</v>
       </c>
       <c r="J66" s="0">
         <v>536.43460000000005</v>
@@ -3889,7 +4558,7 @@
         <v>111</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>306</v>
+        <v>624</v>
       </c>
       <c r="J67" s="0">
         <v>533.26229999999998</v>
@@ -3921,7 +4590,7 @@
         <v>112</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>307</v>
+        <v>625</v>
       </c>
       <c r="J68" s="0">
         <v>523.20399999999995</v>
@@ -3953,7 +4622,7 @@
         <v>113</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>308</v>
+        <v>626</v>
       </c>
       <c r="J69" s="0">
         <v>516.61569999999995</v>
@@ -3985,7 +4654,7 @@
         <v>114</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>309</v>
+        <v>627</v>
       </c>
       <c r="J70" s="0">
         <v>479.05590000000001</v>
@@ -4017,7 +4686,7 @@
         <v>115</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>310</v>
+        <v>628</v>
       </c>
       <c r="J71" s="0">
         <v>442.88510000000002</v>
@@ -4049,7 +4718,7 @@
         <v>116</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>311</v>
+        <v>629</v>
       </c>
       <c r="J72" s="0">
         <v>384.4887</v>
@@ -4081,7 +4750,7 @@
         <v>117</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>312</v>
+        <v>630</v>
       </c>
       <c r="J73" s="0">
         <v>341.47399999999999</v>
@@ -4113,7 +4782,7 @@
         <v>118</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>313</v>
+        <v>631</v>
       </c>
       <c r="J74" s="0">
         <v>292.89060000000001</v>
@@ -4145,7 +4814,7 @@
         <v>119</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>314</v>
+        <v>632</v>
       </c>
       <c r="J75" s="0">
         <v>292.57459999999998</v>
@@ -4177,7 +4846,7 @@
         <v>120</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>315</v>
+        <v>633</v>
       </c>
       <c r="J76" s="0">
         <v>284.52800000000002</v>
@@ -4209,7 +4878,7 @@
         <v>61</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>316</v>
+        <v>634</v>
       </c>
       <c r="J77" s="0">
         <v>284.25450000000001</v>
@@ -4241,7 +4910,7 @@
         <v>121</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>317</v>
+        <v>635</v>
       </c>
       <c r="J78" s="0">
         <v>279.87459999999999</v>
@@ -4273,7 +4942,7 @@
         <v>122</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>318</v>
+        <v>636</v>
       </c>
       <c r="J79" s="0">
         <v>268.24270000000001</v>
@@ -4305,7 +4974,7 @@
         <v>443</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>529</v>
+        <v>637</v>
       </c>
       <c r="J80" s="0">
         <v>10499.483399999999</v>
@@ -4337,7 +5006,7 @@
         <v>444</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>530</v>
+        <v>638</v>
       </c>
       <c r="J81" s="0">
         <v>9639.3300999999992</v>
@@ -4369,7 +5038,7 @@
         <v>447</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>533</v>
+        <v>639</v>
       </c>
       <c r="J82" s="0">
         <v>388.74549999999999</v>
@@ -4401,7 +5070,7 @@
         <v>448</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>534</v>
+        <v>640</v>
       </c>
       <c r="J83" s="0">
         <v>308.16899999999998</v>
@@ -4433,7 +5102,7 @@
         <v>449</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>535</v>
+        <v>641</v>
       </c>
       <c r="J84" s="0">
         <v>305.76100000000002</v>
@@ -4465,7 +5134,7 @@
         <v>451</v>
       </c>
       <c r="I85" s="0" t="s">
-        <v>537</v>
+        <v>642</v>
       </c>
       <c r="J85" s="0">
         <v>297.43759999999998</v>
@@ -4497,7 +5166,7 @@
         <v>452</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>538</v>
+        <v>643</v>
       </c>
       <c r="J86" s="0">
         <v>283.1619</v>
@@ -4529,7 +5198,7 @@
         <v>453</v>
       </c>
       <c r="I87" s="0" t="s">
-        <v>539</v>
+        <v>644</v>
       </c>
       <c r="J87" s="0">
         <v>247.529</v>
@@ -4561,7 +5230,7 @@
         <v>454</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>540</v>
+        <v>645</v>
       </c>
       <c r="J88" s="0">
         <v>231.5712</v>
@@ -4593,7 +5262,7 @@
         <v>455</v>
       </c>
       <c r="I89" s="0" t="s">
-        <v>541</v>
+        <v>646</v>
       </c>
       <c r="J89" s="0">
         <v>1517.5046</v>
@@ -4625,7 +5294,7 @@
         <v>456</v>
       </c>
       <c r="I90" s="0" t="s">
-        <v>542</v>
+        <v>647</v>
       </c>
       <c r="J90" s="0">
         <v>1414.645</v>
@@ -4657,7 +5326,7 @@
         <v>457</v>
       </c>
       <c r="I91" s="0" t="s">
-        <v>543</v>
+        <v>648</v>
       </c>
       <c r="J91" s="0">
         <v>385.28089999999998</v>
@@ -4689,7 +5358,7 @@
         <v>458</v>
       </c>
       <c r="I92" s="0" t="s">
-        <v>544</v>
+        <v>649</v>
       </c>
       <c r="J92" s="0">
         <v>310.61110000000002</v>
@@ -4721,7 +5390,7 @@
         <v>459</v>
       </c>
       <c r="I93" s="0" t="s">
-        <v>545</v>
+        <v>650</v>
       </c>
       <c r="J93" s="0">
         <v>277.84199999999999</v>
@@ -4753,7 +5422,7 @@
         <v>63</v>
       </c>
       <c r="I94" s="0" t="s">
-        <v>546</v>
+        <v>651</v>
       </c>
       <c r="J94" s="0">
         <v>223.45169999999999</v>
@@ -4785,7 +5454,7 @@
         <v>460</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>547</v>
+        <v>652</v>
       </c>
       <c r="J95" s="0">
         <v>10215.762699999999</v>
@@ -4817,7 +5486,7 @@
         <v>461</v>
       </c>
       <c r="I96" s="0" t="s">
-        <v>548</v>
+        <v>653</v>
       </c>
       <c r="J96" s="0">
         <v>8851.0136999999995</v>
@@ -4849,7 +5518,7 @@
         <v>462</v>
       </c>
       <c r="I97" s="0" t="s">
-        <v>549</v>
+        <v>654</v>
       </c>
       <c r="J97" s="0">
         <v>1106.4232</v>
@@ -4881,7 +5550,7 @@
         <v>463</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>550</v>
+        <v>655</v>
       </c>
       <c r="J98" s="0">
         <v>909.94200000000001</v>
@@ -4913,7 +5582,7 @@
         <v>464</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>551</v>
+        <v>656</v>
       </c>
       <c r="J99" s="0">
         <v>316.77910000000003</v>
@@ -4945,7 +5614,7 @@
         <v>465</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>552</v>
+        <v>657</v>
       </c>
       <c r="J100" s="0">
         <v>284.43700000000001</v>
@@ -4977,7 +5646,7 @@
         <v>466</v>
       </c>
       <c r="I101" s="0" t="s">
-        <v>553</v>
+        <v>658</v>
       </c>
       <c r="J101" s="0">
         <v>282.07659999999999</v>
@@ -5009,7 +5678,7 @@
         <v>467</v>
       </c>
       <c r="I102" s="0" t="s">
-        <v>554</v>
+        <v>659</v>
       </c>
       <c r="J102" s="0">
         <v>261.52760000000001</v>
@@ -5041,7 +5710,7 @@
         <v>468</v>
       </c>
       <c r="I103" s="0" t="s">
-        <v>555</v>
+        <v>660</v>
       </c>
       <c r="J103" s="0">
         <v>248.01570000000001</v>
@@ -5073,7 +5742,7 @@
         <v>469</v>
       </c>
       <c r="I104" s="0" t="s">
-        <v>556</v>
+        <v>661</v>
       </c>
       <c r="J104" s="0">
         <v>246.53380000000001</v>
@@ -5105,7 +5774,7 @@
         <v>470</v>
       </c>
       <c r="I105" s="0" t="s">
-        <v>557</v>
+        <v>662</v>
       </c>
       <c r="J105" s="0">
         <v>228.9768</v>
@@ -5137,7 +5806,7 @@
         <v>471</v>
       </c>
       <c r="I106" s="0" t="s">
-        <v>558</v>
+        <v>663</v>
       </c>
       <c r="J106" s="0">
         <v>216.21680000000001</v>
@@ -5169,7 +5838,7 @@
         <v>123</v>
       </c>
       <c r="I107" s="0" t="s">
-        <v>319</v>
+        <v>664</v>
       </c>
       <c r="J107" s="0">
         <v>10261.8174</v>
@@ -5201,7 +5870,7 @@
         <v>124</v>
       </c>
       <c r="I108" s="0" t="s">
-        <v>320</v>
+        <v>665</v>
       </c>
       <c r="J108" s="0">
         <v>9826.5293000000001</v>
@@ -5233,7 +5902,7 @@
         <v>125</v>
       </c>
       <c r="I109" s="0" t="s">
-        <v>321</v>
+        <v>666</v>
       </c>
       <c r="J109" s="0">
         <v>310.85700000000003</v>
@@ -5265,7 +5934,7 @@
         <v>126</v>
       </c>
       <c r="I110" s="0" t="s">
-        <v>322</v>
+        <v>667</v>
       </c>
       <c r="J110" s="0">
         <v>294.82119999999998</v>
@@ -5297,7 +5966,7 @@
         <v>127</v>
       </c>
       <c r="I111" s="0" t="s">
-        <v>323</v>
+        <v>668</v>
       </c>
       <c r="J111" s="0">
         <v>290.76960000000003</v>
@@ -5329,7 +5998,7 @@
         <v>128</v>
       </c>
       <c r="I112" s="0" t="s">
-        <v>324</v>
+        <v>669</v>
       </c>
       <c r="J112" s="0">
         <v>273.49590000000001</v>
@@ -5361,7 +6030,7 @@
         <v>129</v>
       </c>
       <c r="I113" s="0" t="s">
-        <v>325</v>
+        <v>670</v>
       </c>
       <c r="J113" s="0">
         <v>242.22909999999999</v>
@@ -5393,7 +6062,7 @@
         <v>130</v>
       </c>
       <c r="I114" s="0" t="s">
-        <v>326</v>
+        <v>671</v>
       </c>
       <c r="J114" s="0">
         <v>238.70050000000001</v>
@@ -5425,7 +6094,7 @@
         <v>131</v>
       </c>
       <c r="I115" s="0" t="s">
-        <v>327</v>
+        <v>672</v>
       </c>
       <c r="J115" s="0">
         <v>227.2551</v>
@@ -5457,7 +6126,7 @@
         <v>132</v>
       </c>
       <c r="I116" s="0" t="s">
-        <v>328</v>
+        <v>673</v>
       </c>
       <c r="J116" s="0">
         <v>214.56540000000001</v>
@@ -5489,7 +6158,7 @@
         <v>133</v>
       </c>
       <c r="I117" s="0" t="s">
-        <v>329</v>
+        <v>674</v>
       </c>
       <c r="J117" s="0">
         <v>9905.6357000000007</v>
@@ -5521,7 +6190,7 @@
         <v>134</v>
       </c>
       <c r="I118" s="0" t="s">
-        <v>330</v>
+        <v>675</v>
       </c>
       <c r="J118" s="0">
         <v>8499.6309000000001</v>
@@ -5553,7 +6222,7 @@
         <v>135</v>
       </c>
       <c r="I119" s="0" t="s">
-        <v>331</v>
+        <v>676</v>
       </c>
       <c r="J119" s="0">
         <v>1404.5636</v>
@@ -5585,7 +6254,7 @@
         <v>136</v>
       </c>
       <c r="I120" s="0" t="s">
-        <v>332</v>
+        <v>677</v>
       </c>
       <c r="J120" s="0">
         <v>315.27960000000002</v>
@@ -5617,7 +6286,7 @@
         <v>137</v>
       </c>
       <c r="I121" s="0" t="s">
-        <v>333</v>
+        <v>678</v>
       </c>
       <c r="J121" s="0">
         <v>302.22129999999999</v>
@@ -5649,7 +6318,7 @@
         <v>138</v>
       </c>
       <c r="I122" s="0" t="s">
-        <v>334</v>
+        <v>679</v>
       </c>
       <c r="J122" s="0">
         <v>266.9862</v>
@@ -5681,7 +6350,7 @@
         <v>139</v>
       </c>
       <c r="I123" s="0" t="s">
-        <v>335</v>
+        <v>680</v>
       </c>
       <c r="J123" s="0">
         <v>264.11059999999998</v>
@@ -5713,7 +6382,7 @@
         <v>140</v>
       </c>
       <c r="I124" s="0" t="s">
-        <v>336</v>
+        <v>681</v>
       </c>
       <c r="J124" s="0">
         <v>247.79859999999999</v>
@@ -5745,7 +6414,7 @@
         <v>141</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>337</v>
+        <v>682</v>
       </c>
       <c r="J125" s="0">
         <v>239.36019999999999</v>
@@ -5777,7 +6446,7 @@
         <v>142</v>
       </c>
       <c r="I126" s="0" t="s">
-        <v>338</v>
+        <v>683</v>
       </c>
       <c r="J126" s="0">
         <v>208.72989999999999</v>
@@ -5809,7 +6478,7 @@
         <v>143</v>
       </c>
       <c r="I127" s="0" t="s">
-        <v>339</v>
+        <v>684</v>
       </c>
       <c r="J127" s="0">
         <v>199.44909999999999</v>
@@ -5841,7 +6510,7 @@
         <v>144</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>340</v>
+        <v>685</v>
       </c>
       <c r="J128" s="0">
         <v>9596.9883000000009</v>
@@ -5873,7 +6542,7 @@
         <v>145</v>
       </c>
       <c r="I129" s="0" t="s">
-        <v>341</v>
+        <v>686</v>
       </c>
       <c r="J129" s="0">
         <v>8798.1787000000004</v>
@@ -5905,7 +6574,7 @@
         <v>146</v>
       </c>
       <c r="I130" s="0" t="s">
-        <v>342</v>
+        <v>687</v>
       </c>
       <c r="J130" s="0">
         <v>1321.1365000000001</v>
@@ -5937,7 +6606,7 @@
         <v>147</v>
       </c>
       <c r="I131" s="0" t="s">
-        <v>343</v>
+        <v>688</v>
       </c>
       <c r="J131" s="0">
         <v>959.9144</v>
@@ -5969,7 +6638,7 @@
         <v>148</v>
       </c>
       <c r="I132" s="0" t="s">
-        <v>344</v>
+        <v>689</v>
       </c>
       <c r="J132" s="0">
         <v>309.23169999999999</v>
@@ -6001,7 +6670,7 @@
         <v>149</v>
       </c>
       <c r="I133" s="0" t="s">
-        <v>345</v>
+        <v>690</v>
       </c>
       <c r="J133" s="0">
         <v>301.12470000000002</v>
@@ -6033,7 +6702,7 @@
         <v>150</v>
       </c>
       <c r="I134" s="0" t="s">
-        <v>346</v>
+        <v>691</v>
       </c>
       <c r="J134" s="0">
         <v>296.84010000000001</v>
@@ -6065,7 +6734,7 @@
         <v>151</v>
       </c>
       <c r="I135" s="0" t="s">
-        <v>347</v>
+        <v>692</v>
       </c>
       <c r="J135" s="0">
         <v>288.2115</v>
@@ -6097,7 +6766,7 @@
         <v>152</v>
       </c>
       <c r="I136" s="0" t="s">
-        <v>348</v>
+        <v>693</v>
       </c>
       <c r="J136" s="0">
         <v>274.3639</v>
@@ -6129,7 +6798,7 @@
         <v>153</v>
       </c>
       <c r="I137" s="0" t="s">
-        <v>349</v>
+        <v>694</v>
       </c>
       <c r="J137" s="0">
         <v>260.00229999999999</v>
@@ -6161,7 +6830,7 @@
         <v>154</v>
       </c>
       <c r="I138" s="0" t="s">
-        <v>350</v>
+        <v>695</v>
       </c>
       <c r="J138" s="0">
         <v>246.21190000000001</v>
@@ -6193,7 +6862,7 @@
         <v>155</v>
       </c>
       <c r="I139" s="0" t="s">
-        <v>351</v>
+        <v>696</v>
       </c>
       <c r="J139" s="0">
         <v>180.47190000000001</v>
@@ -6225,7 +6894,7 @@
         <v>156</v>
       </c>
       <c r="I140" s="0" t="s">
-        <v>352</v>
+        <v>697</v>
       </c>
       <c r="J140" s="0">
         <v>9836.6807000000008</v>
@@ -6257,7 +6926,7 @@
         <v>158</v>
       </c>
       <c r="I141" s="0" t="s">
-        <v>354</v>
+        <v>698</v>
       </c>
       <c r="J141" s="0">
         <v>908.87840000000006</v>
@@ -6289,7 +6958,7 @@
         <v>159</v>
       </c>
       <c r="I142" s="0" t="s">
-        <v>355</v>
+        <v>699</v>
       </c>
       <c r="J142" s="0">
         <v>840.46699999999999</v>
@@ -6321,7 +6990,7 @@
         <v>160</v>
       </c>
       <c r="I143" s="0" t="s">
-        <v>356</v>
+        <v>700</v>
       </c>
       <c r="J143" s="0">
         <v>385.22919999999999</v>
@@ -6353,7 +7022,7 @@
         <v>161</v>
       </c>
       <c r="I144" s="0" t="s">
-        <v>357</v>
+        <v>701</v>
       </c>
       <c r="J144" s="0">
         <v>310.47890000000001</v>
@@ -6385,7 +7054,7 @@
         <v>162</v>
       </c>
       <c r="I145" s="0" t="s">
-        <v>358</v>
+        <v>702</v>
       </c>
       <c r="J145" s="0">
         <v>300.91699999999997</v>
@@ -6417,7 +7086,7 @@
         <v>163</v>
       </c>
       <c r="I146" s="0" t="s">
-        <v>359</v>
+        <v>703</v>
       </c>
       <c r="J146" s="0">
         <v>285.7113</v>
@@ -6449,7 +7118,7 @@
         <v>164</v>
       </c>
       <c r="I147" s="0" t="s">
-        <v>360</v>
+        <v>704</v>
       </c>
       <c r="J147" s="0">
         <v>255.1182</v>
@@ -6481,7 +7150,7 @@
         <v>165</v>
       </c>
       <c r="I148" s="0" t="s">
-        <v>361</v>
+        <v>705</v>
       </c>
       <c r="J148" s="0">
         <v>251.63229999999999</v>
@@ -6513,7 +7182,7 @@
         <v>166</v>
       </c>
       <c r="I149" s="0" t="s">
-        <v>362</v>
+        <v>706</v>
       </c>
       <c r="J149" s="0">
         <v>241.47989999999999</v>
@@ -6545,7 +7214,7 @@
         <v>167</v>
       </c>
       <c r="I150" s="0" t="s">
-        <v>363</v>
+        <v>707</v>
       </c>
       <c r="J150" s="0">
         <v>239.88820000000001</v>
@@ -6577,7 +7246,7 @@
         <v>168</v>
       </c>
       <c r="I151" s="0" t="s">
-        <v>364</v>
+        <v>708</v>
       </c>
       <c r="J151" s="0">
         <v>10661.891600000001</v>
@@ -6609,7 +7278,7 @@
         <v>169</v>
       </c>
       <c r="I152" s="0" t="s">
-        <v>365</v>
+        <v>709</v>
       </c>
       <c r="J152" s="0">
         <v>7643.7520000000004</v>
@@ -6641,7 +7310,7 @@
         <v>170</v>
       </c>
       <c r="I153" s="0" t="s">
-        <v>366</v>
+        <v>710</v>
       </c>
       <c r="J153" s="0">
         <v>1539.2754</v>
@@ -6673,7 +7342,7 @@
         <v>171</v>
       </c>
       <c r="I154" s="0" t="s">
-        <v>367</v>
+        <v>711</v>
       </c>
       <c r="J154" s="0">
         <v>1393.9193</v>
@@ -6705,7 +7374,7 @@
         <v>172</v>
       </c>
       <c r="I155" s="0" t="s">
-        <v>368</v>
+        <v>712</v>
       </c>
       <c r="J155" s="0">
         <v>457.66739999999999</v>
@@ -6737,7 +7406,7 @@
         <v>173</v>
       </c>
       <c r="I156" s="0" t="s">
-        <v>369</v>
+        <v>713</v>
       </c>
       <c r="J156" s="0">
         <v>419.16669999999999</v>
@@ -6769,7 +7438,7 @@
         <v>174</v>
       </c>
       <c r="I157" s="0" t="s">
-        <v>370</v>
+        <v>714</v>
       </c>
       <c r="J157" s="0">
         <v>417.49169999999998</v>
@@ -6801,7 +7470,7 @@
         <v>175</v>
       </c>
       <c r="I158" s="0" t="s">
-        <v>371</v>
+        <v>715</v>
       </c>
       <c r="J158" s="0">
         <v>399.00799999999998</v>
@@ -6833,7 +7502,7 @@
         <v>176</v>
       </c>
       <c r="I159" s="0" t="s">
-        <v>372</v>
+        <v>716</v>
       </c>
       <c r="J159" s="0">
         <v>361.1662</v>
@@ -6865,7 +7534,7 @@
         <v>178</v>
       </c>
       <c r="I160" s="0" t="s">
-        <v>374</v>
+        <v>717</v>
       </c>
       <c r="J160" s="0">
         <v>311.19600000000003</v>
@@ -6897,7 +7566,7 @@
         <v>179</v>
       </c>
       <c r="I161" s="0" t="s">
-        <v>375</v>
+        <v>718</v>
       </c>
       <c r="J161" s="0">
         <v>291.23480000000001</v>
@@ -6929,7 +7598,7 @@
         <v>180</v>
       </c>
       <c r="I162" s="0" t="s">
-        <v>376</v>
+        <v>719</v>
       </c>
       <c r="J162" s="0">
         <v>9127.5985999999994</v>
@@ -6961,7 +7630,7 @@
         <v>181</v>
       </c>
       <c r="I163" s="0" t="s">
-        <v>377</v>
+        <v>720</v>
       </c>
       <c r="J163" s="0">
         <v>8554.8642999999993</v>
@@ -6993,7 +7662,7 @@
         <v>182</v>
       </c>
       <c r="I164" s="0" t="s">
-        <v>378</v>
+        <v>721</v>
       </c>
       <c r="J164" s="0">
         <v>1414.848</v>
@@ -7025,7 +7694,7 @@
         <v>183</v>
       </c>
       <c r="I165" s="0" t="s">
-        <v>379</v>
+        <v>722</v>
       </c>
       <c r="J165" s="0">
         <v>752.67660000000001</v>
@@ -7057,7 +7726,7 @@
         <v>184</v>
       </c>
       <c r="I166" s="0" t="s">
-        <v>380</v>
+        <v>723</v>
       </c>
       <c r="J166" s="0">
         <v>348.73090000000002</v>
@@ -7089,7 +7758,7 @@
         <v>185</v>
       </c>
       <c r="I167" s="0" t="s">
-        <v>381</v>
+        <v>724</v>
       </c>
       <c r="J167" s="0">
         <v>307.04939999999999</v>
@@ -7121,7 +7790,7 @@
         <v>186</v>
       </c>
       <c r="I168" s="0" t="s">
-        <v>382</v>
+        <v>725</v>
       </c>
       <c r="J168" s="0">
         <v>280.97919999999999</v>
@@ -7153,7 +7822,7 @@
         <v>187</v>
       </c>
       <c r="I169" s="0" t="s">
-        <v>383</v>
+        <v>726</v>
       </c>
       <c r="J169" s="0">
         <v>265.1284</v>
@@ -7185,7 +7854,7 @@
         <v>188</v>
       </c>
       <c r="I170" s="0" t="s">
-        <v>384</v>
+        <v>727</v>
       </c>
       <c r="J170" s="0">
         <v>249.8895</v>
@@ -7217,7 +7886,7 @@
         <v>189</v>
       </c>
       <c r="I171" s="0" t="s">
-        <v>385</v>
+        <v>728</v>
       </c>
       <c r="J171" s="0">
         <v>215.3955</v>
@@ -7249,7 +7918,7 @@
         <v>190</v>
       </c>
       <c r="I172" s="0" t="s">
-        <v>386</v>
+        <v>729</v>
       </c>
       <c r="J172" s="0">
         <v>213.6302</v>
@@ -7281,7 +7950,7 @@
         <v>191</v>
       </c>
       <c r="I173" s="0" t="s">
-        <v>387</v>
+        <v>730</v>
       </c>
       <c r="J173" s="0">
         <v>193.54920000000001</v>
@@ -7313,7 +7982,7 @@
         <v>192</v>
       </c>
       <c r="I174" s="0" t="s">
-        <v>388</v>
+        <v>731</v>
       </c>
       <c r="J174" s="0">
         <v>9254.9814000000006</v>
@@ -7345,7 +8014,7 @@
         <v>193</v>
       </c>
       <c r="I175" s="0" t="s">
-        <v>389</v>
+        <v>732</v>
       </c>
       <c r="J175" s="0">
         <v>8396.3974999999991</v>
@@ -7377,7 +8046,7 @@
         <v>194</v>
       </c>
       <c r="I176" s="0" t="s">
-        <v>390</v>
+        <v>733</v>
       </c>
       <c r="J176" s="0">
         <v>1087.1931999999999</v>
@@ -7409,7 +8078,7 @@
         <v>195</v>
       </c>
       <c r="I177" s="0" t="s">
-        <v>391</v>
+        <v>734</v>
       </c>
       <c r="J177" s="0">
         <v>1026.0048999999999</v>
@@ -7441,7 +8110,7 @@
         <v>196</v>
       </c>
       <c r="I178" s="0" t="s">
-        <v>392</v>
+        <v>735</v>
       </c>
       <c r="J178" s="0">
         <v>328.2697</v>
@@ -7473,7 +8142,7 @@
         <v>197</v>
       </c>
       <c r="I179" s="0" t="s">
-        <v>393</v>
+        <v>736</v>
       </c>
       <c r="J179" s="0">
         <v>306.13749999999999</v>
@@ -7505,7 +8174,7 @@
         <v>198</v>
       </c>
       <c r="I180" s="0" t="s">
-        <v>394</v>
+        <v>737</v>
       </c>
       <c r="J180" s="0">
         <v>302.69369999999998</v>
@@ -7537,7 +8206,7 @@
         <v>199</v>
       </c>
       <c r="I181" s="0" t="s">
-        <v>395</v>
+        <v>738</v>
       </c>
       <c r="J181" s="0">
         <v>296.63529999999997</v>
@@ -7569,7 +8238,7 @@
         <v>200</v>
       </c>
       <c r="I182" s="0" t="s">
-        <v>396</v>
+        <v>739</v>
       </c>
       <c r="J182" s="0">
         <v>292.96969999999999</v>
@@ -7601,7 +8270,7 @@
         <v>201</v>
       </c>
       <c r="I183" s="0" t="s">
-        <v>397</v>
+        <v>740</v>
       </c>
       <c r="J183" s="0">
         <v>267.35629999999998</v>
@@ -7633,7 +8302,7 @@
         <v>203</v>
       </c>
       <c r="I184" s="0" t="s">
-        <v>399</v>
+        <v>741</v>
       </c>
       <c r="J184" s="0">
         <v>165.21969999999999</v>
@@ -7665,7 +8334,7 @@
         <v>206</v>
       </c>
       <c r="I185" s="0" t="s">
-        <v>402</v>
+        <v>742</v>
       </c>
       <c r="J185" s="0">
         <v>1713.3430000000001</v>
@@ -7697,7 +8366,7 @@
         <v>207</v>
       </c>
       <c r="I186" s="0" t="s">
-        <v>403</v>
+        <v>743</v>
       </c>
       <c r="J186" s="0">
         <v>1254.9603</v>
@@ -7729,7 +8398,7 @@
         <v>208</v>
       </c>
       <c r="I187" s="0" t="s">
-        <v>404</v>
+        <v>744</v>
       </c>
       <c r="J187" s="0">
         <v>412.1336</v>
@@ -7761,7 +8430,7 @@
         <v>209</v>
       </c>
       <c r="I188" s="0" t="s">
-        <v>405</v>
+        <v>745</v>
       </c>
       <c r="J188" s="0">
         <v>395.3304</v>
@@ -7793,7 +8462,7 @@
         <v>210</v>
       </c>
       <c r="I189" s="0" t="s">
-        <v>406</v>
+        <v>746</v>
       </c>
       <c r="J189" s="0">
         <v>314.40159999999997</v>
@@ -7825,7 +8494,7 @@
         <v>211</v>
       </c>
       <c r="I190" s="0" t="s">
-        <v>407</v>
+        <v>747</v>
       </c>
       <c r="J190" s="0">
         <v>306.70960000000002</v>
@@ -7857,7 +8526,7 @@
         <v>212</v>
       </c>
       <c r="I191" s="0" t="s">
-        <v>408</v>
+        <v>748</v>
       </c>
       <c r="J191" s="0">
         <v>285.86070000000001</v>
@@ -7889,7 +8558,7 @@
         <v>213</v>
       </c>
       <c r="I192" s="0" t="s">
-        <v>409</v>
+        <v>749</v>
       </c>
       <c r="J192" s="0">
         <v>284.4486</v>
@@ -7921,7 +8590,7 @@
         <v>214</v>
       </c>
       <c r="I193" s="0" t="s">
-        <v>410</v>
+        <v>750</v>
       </c>
       <c r="J193" s="0">
         <v>281.97449999999998</v>
@@ -7953,7 +8622,7 @@
         <v>216</v>
       </c>
       <c r="I194" s="0" t="s">
-        <v>412</v>
+        <v>751</v>
       </c>
       <c r="J194" s="0">
         <v>9423.6895000000004</v>
@@ -7985,7 +8654,7 @@
         <v>217</v>
       </c>
       <c r="I195" s="0" t="s">
-        <v>413</v>
+        <v>752</v>
       </c>
       <c r="J195" s="0">
         <v>9234.3525000000009</v>
@@ -8017,7 +8686,7 @@
         <v>218</v>
       </c>
       <c r="I196" s="0" t="s">
-        <v>414</v>
+        <v>753</v>
       </c>
       <c r="J196" s="0">
         <v>1208.9946</v>
@@ -8049,7 +8718,7 @@
         <v>219</v>
       </c>
       <c r="I197" s="0" t="s">
-        <v>415</v>
+        <v>754</v>
       </c>
       <c r="J197" s="0">
         <v>951.19749999999999</v>
@@ -8081,7 +8750,7 @@
         <v>220</v>
       </c>
       <c r="I198" s="0" t="s">
-        <v>416</v>
+        <v>755</v>
       </c>
       <c r="J198" s="0">
         <v>316.12619999999998</v>
@@ -8113,7 +8782,7 @@
         <v>221</v>
       </c>
       <c r="I199" s="0" t="s">
-        <v>417</v>
+        <v>756</v>
       </c>
       <c r="J199" s="0">
         <v>302.2124</v>
@@ -8145,7 +8814,7 @@
         <v>222</v>
       </c>
       <c r="I200" s="0" t="s">
-        <v>418</v>
+        <v>757</v>
       </c>
       <c r="J200" s="0">
         <v>294.96859999999998</v>
@@ -8177,7 +8846,7 @@
         <v>223</v>
       </c>
       <c r="I201" s="0" t="s">
-        <v>419</v>
+        <v>758</v>
       </c>
       <c r="J201" s="0">
         <v>291.27109999999999</v>
@@ -8209,7 +8878,7 @@
         <v>224</v>
       </c>
       <c r="I202" s="0" t="s">
-        <v>420</v>
+        <v>759</v>
       </c>
       <c r="J202" s="0">
         <v>264.68939999999998</v>
@@ -8241,7 +8910,7 @@
         <v>225</v>
       </c>
       <c r="I203" s="0" t="s">
-        <v>421</v>
+        <v>760</v>
       </c>
       <c r="J203" s="0">
         <v>257.6934</v>
@@ -8273,7 +8942,7 @@
         <v>226</v>
       </c>
       <c r="I204" s="0" t="s">
-        <v>422</v>
+        <v>761</v>
       </c>
       <c r="J204" s="0">
         <v>214.37610000000001</v>
@@ -8305,7 +8974,7 @@
         <v>227</v>
       </c>
       <c r="I205" s="0" t="s">
-        <v>423</v>
+        <v>762</v>
       </c>
       <c r="J205" s="0">
         <v>190.58150000000001</v>
@@ -8337,7 +9006,7 @@
         <v>228</v>
       </c>
       <c r="I206" s="0" t="s">
-        <v>424</v>
+        <v>763</v>
       </c>
       <c r="J206" s="0">
         <v>10441.448200000001</v>
@@ -8369,7 +9038,7 @@
         <v>229</v>
       </c>
       <c r="I207" s="0" t="s">
-        <v>425</v>
+        <v>764</v>
       </c>
       <c r="J207" s="0">
         <v>9728.8516</v>
@@ -8401,7 +9070,7 @@
         <v>230</v>
       </c>
       <c r="I208" s="0" t="s">
-        <v>426</v>
+        <v>765</v>
       </c>
       <c r="J208" s="0">
         <v>1533.4409000000001</v>
@@ -8433,7 +9102,7 @@
         <v>231</v>
       </c>
       <c r="I209" s="0" t="s">
-        <v>427</v>
+        <v>766</v>
       </c>
       <c r="J209" s="0">
         <v>1358.2428</v>
@@ -8465,7 +9134,7 @@
         <v>232</v>
       </c>
       <c r="I210" s="0" t="s">
-        <v>428</v>
+        <v>767</v>
       </c>
       <c r="J210" s="0">
         <v>452.1069</v>
@@ -8497,7 +9166,7 @@
         <v>233</v>
       </c>
       <c r="I211" s="0" t="s">
-        <v>429</v>
+        <v>768</v>
       </c>
       <c r="J211" s="0">
         <v>439.75790000000001</v>
@@ -8529,7 +9198,7 @@
         <v>234</v>
       </c>
       <c r="I212" s="0" t="s">
-        <v>430</v>
+        <v>769</v>
       </c>
       <c r="J212" s="0">
         <v>376.52229999999997</v>
@@ -8561,7 +9230,7 @@
         <v>235</v>
       </c>
       <c r="I213" s="0" t="s">
-        <v>431</v>
+        <v>770</v>
       </c>
       <c r="J213" s="0">
         <v>375.43979999999999</v>
@@ -8593,7 +9262,7 @@
         <v>236</v>
       </c>
       <c r="I214" s="0" t="s">
-        <v>432</v>
+        <v>771</v>
       </c>
       <c r="J214" s="0">
         <v>373.55439999999999</v>
@@ -8625,7 +9294,7 @@
         <v>237</v>
       </c>
       <c r="I215" s="0" t="s">
-        <v>433</v>
+        <v>772</v>
       </c>
       <c r="J215" s="0">
         <v>302.76659999999998</v>
@@ -8657,7 +9326,7 @@
         <v>238</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>434</v>
+        <v>773</v>
       </c>
       <c r="J216" s="0">
         <v>300.86579999999998</v>
@@ -8689,7 +9358,7 @@
         <v>472</v>
       </c>
       <c r="I217" s="0" t="s">
-        <v>514</v>
+        <v>774</v>
       </c>
       <c r="J217" s="0">
         <v>12892.7021</v>
@@ -8721,7 +9390,7 @@
         <v>473</v>
       </c>
       <c r="I218" s="0" t="s">
-        <v>515</v>
+        <v>775</v>
       </c>
       <c r="J218" s="0">
         <v>10694.238300000001</v>
@@ -8753,7 +9422,7 @@
         <v>474</v>
       </c>
       <c r="I219" s="0" t="s">
-        <v>516</v>
+        <v>776</v>
       </c>
       <c r="J219" s="0">
         <v>2047.9614999999999</v>
@@ -8785,7 +9454,7 @@
         <v>475</v>
       </c>
       <c r="I220" s="0" t="s">
-        <v>517</v>
+        <v>777</v>
       </c>
       <c r="J220" s="0">
         <v>910.678</v>
@@ -8817,7 +9486,7 @@
         <v>477</v>
       </c>
       <c r="I221" s="0" t="s">
-        <v>519</v>
+        <v>778</v>
       </c>
       <c r="J221" s="0">
         <v>568.2056</v>
@@ -8849,7 +9518,7 @@
         <v>479</v>
       </c>
       <c r="I222" s="0" t="s">
-        <v>521</v>
+        <v>779</v>
       </c>
       <c r="J222" s="0">
         <v>489.4178</v>
@@ -8881,7 +9550,7 @@
         <v>481</v>
       </c>
       <c r="I223" s="0" t="s">
-        <v>523</v>
+        <v>780</v>
       </c>
       <c r="J223" s="0">
         <v>370.15899999999999</v>
@@ -8913,7 +9582,7 @@
         <v>483</v>
       </c>
       <c r="I224" s="0" t="s">
-        <v>525</v>
+        <v>781</v>
       </c>
       <c r="J224" s="0">
         <v>340.95030000000003</v>

--- a/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="51298" uniqueCount="782">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="123910" uniqueCount="782">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="123910" uniqueCount="782">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="127944" uniqueCount="782">
   <si>
     <t>Year</t>
   </si>
@@ -2408,16 +2408,16 @@
   <dimension ref="A1:J238"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" customWidth="true"/>
-    <col min="2" max="2" width="7" customWidth="true"/>
-    <col min="3" max="3" width="11.28515625" customWidth="true"/>
-    <col min="4" max="4" width="18.28515625" customWidth="true"/>
-    <col min="5" max="5" width="12.7109375" customWidth="true"/>
-    <col min="6" max="6" width="13" customWidth="true"/>
-    <col min="7" max="7" width="8.5703125" customWidth="true"/>
-    <col min="8" max="8" width="37.42578125" customWidth="true"/>
-    <col min="9" max="9" width="148" customWidth="true"/>
-    <col min="10" max="10" width="10.7109375" customWidth="true"/>
+    <col min="1" max="1" width="14.08984375" customWidth="true"/>
+    <col min="2" max="2" width="6.54296875" customWidth="true"/>
+    <col min="3" max="3" width="10.36328125" customWidth="true"/>
+    <col min="4" max="4" width="17.36328125" customWidth="true"/>
+    <col min="5" max="5" width="11.81640625" customWidth="true"/>
+    <col min="6" max="6" width="11.90625" customWidth="true"/>
+    <col min="7" max="7" width="7.90625" customWidth="true"/>
+    <col min="8" max="8" width="36.26953125" customWidth="true"/>
+    <col min="9" max="9" width="168.54296875" customWidth="true"/>
+    <col min="10" max="10" width="10.453125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2478,7 +2478,7 @@
         <v>46</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>559</v>
+        <v>241</v>
       </c>
       <c r="J2" s="0">
         <v>9347.0458999999992</v>
@@ -2510,7 +2510,7 @@
         <v>47</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>560</v>
+        <v>242</v>
       </c>
       <c r="J3" s="0">
         <v>9278.2314000000006</v>
@@ -2542,7 +2542,7 @@
         <v>48</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>561</v>
+        <v>243</v>
       </c>
       <c r="J4" s="0">
         <v>1582.4756</v>
@@ -2574,7 +2574,7 @@
         <v>49</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>562</v>
+        <v>244</v>
       </c>
       <c r="J5" s="0">
         <v>1241.5624</v>
@@ -2606,7 +2606,7 @@
         <v>50</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>563</v>
+        <v>245</v>
       </c>
       <c r="J6" s="0">
         <v>421.89870000000002</v>
@@ -2638,7 +2638,7 @@
         <v>51</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>564</v>
+        <v>246</v>
       </c>
       <c r="J7" s="0">
         <v>398.66129999999998</v>
@@ -2670,7 +2670,7 @@
         <v>52</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>565</v>
+        <v>247</v>
       </c>
       <c r="J8" s="0">
         <v>328.8254</v>
@@ -2702,7 +2702,7 @@
         <v>53</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>566</v>
+        <v>248</v>
       </c>
       <c r="J9" s="0">
         <v>313.2783</v>
@@ -2734,7 +2734,7 @@
         <v>54</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>567</v>
+        <v>249</v>
       </c>
       <c r="J10" s="0">
         <v>295.0641</v>
@@ -2766,7 +2766,7 @@
         <v>55</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>568</v>
+        <v>250</v>
       </c>
       <c r="J11" s="0">
         <v>294.86309999999998</v>
@@ -2798,7 +2798,7 @@
         <v>56</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>569</v>
+        <v>251</v>
       </c>
       <c r="J12" s="0">
         <v>281.74770000000001</v>
@@ -2830,7 +2830,7 @@
         <v>57</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>570</v>
+        <v>252</v>
       </c>
       <c r="J13" s="0">
         <v>274.15789999999998</v>
@@ -2862,7 +2862,7 @@
         <v>58</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>571</v>
+        <v>253</v>
       </c>
       <c r="J14" s="0">
         <v>370.1397</v>
@@ -2894,7 +2894,7 @@
         <v>59</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>572</v>
+        <v>254</v>
       </c>
       <c r="J15" s="0">
         <v>292.09550000000002</v>
@@ -2926,7 +2926,7 @@
         <v>60</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>573</v>
+        <v>255</v>
       </c>
       <c r="J16" s="0">
         <v>289.81389999999999</v>
@@ -2958,7 +2958,7 @@
         <v>61</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>574</v>
+        <v>256</v>
       </c>
       <c r="J17" s="0">
         <v>284.25450000000001</v>
@@ -2990,7 +2990,7 @@
         <v>62</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>575</v>
+        <v>257</v>
       </c>
       <c r="J18" s="0">
         <v>242.2781</v>
@@ -3022,7 +3022,7 @@
         <v>63</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>576</v>
+        <v>258</v>
       </c>
       <c r="J19" s="0">
         <v>223.45169999999999</v>
@@ -3054,7 +3054,7 @@
         <v>64</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>577</v>
+        <v>259</v>
       </c>
       <c r="J20" s="0">
         <v>199.1625</v>
@@ -3086,7 +3086,7 @@
         <v>65</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>578</v>
+        <v>260</v>
       </c>
       <c r="J21" s="0">
         <v>194.94929999999999</v>
@@ -3118,7 +3118,7 @@
         <v>66</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>579</v>
+        <v>261</v>
       </c>
       <c r="J22" s="0">
         <v>347.25940000000003</v>
@@ -3150,7 +3150,7 @@
         <v>67</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>580</v>
+        <v>262</v>
       </c>
       <c r="J23" s="0">
         <v>331.1694</v>
@@ -3182,7 +3182,7 @@
         <v>68</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>581</v>
+        <v>263</v>
       </c>
       <c r="J24" s="0">
         <v>321.93639999999999</v>
@@ -3214,7 +3214,7 @@
         <v>69</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>582</v>
+        <v>264</v>
       </c>
       <c r="J25" s="0">
         <v>277.89530000000002</v>
@@ -3246,7 +3246,7 @@
         <v>70</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>583</v>
+        <v>265</v>
       </c>
       <c r="J26" s="0">
         <v>276.74470000000002</v>
@@ -3278,7 +3278,7 @@
         <v>71</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>584</v>
+        <v>266</v>
       </c>
       <c r="J27" s="0">
         <v>268.73340000000002</v>
@@ -3310,7 +3310,7 @@
         <v>72</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>585</v>
+        <v>267</v>
       </c>
       <c r="J28" s="0">
         <v>267.4108</v>
@@ -3342,7 +3342,7 @@
         <v>73</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>586</v>
+        <v>268</v>
       </c>
       <c r="J29" s="0">
         <v>246.4597</v>
@@ -3374,7 +3374,7 @@
         <v>74</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>587</v>
+        <v>269</v>
       </c>
       <c r="J30" s="0">
         <v>9973.1728999999996</v>
@@ -3406,7 +3406,7 @@
         <v>75</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>588</v>
+        <v>270</v>
       </c>
       <c r="J31" s="0">
         <v>8216.1016</v>
@@ -3438,7 +3438,7 @@
         <v>76</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>589</v>
+        <v>271</v>
       </c>
       <c r="J32" s="0">
         <v>381.02080000000001</v>
@@ -3470,7 +3470,7 @@
         <v>77</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>590</v>
+        <v>272</v>
       </c>
       <c r="J33" s="0">
         <v>329.35809999999998</v>
@@ -3502,7 +3502,7 @@
         <v>78</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>591</v>
+        <v>273</v>
       </c>
       <c r="J34" s="0">
         <v>298.96679999999998</v>
@@ -3534,7 +3534,7 @@
         <v>79</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>592</v>
+        <v>274</v>
       </c>
       <c r="J35" s="0">
         <v>290.85469999999998</v>
@@ -3566,7 +3566,7 @@
         <v>80</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>593</v>
+        <v>275</v>
       </c>
       <c r="J36" s="0">
         <v>260.34840000000003</v>
@@ -3598,7 +3598,7 @@
         <v>81</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>594</v>
+        <v>276</v>
       </c>
       <c r="J37" s="0">
         <v>243.72470000000001</v>
@@ -3630,7 +3630,7 @@
         <v>82</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>595</v>
+        <v>277</v>
       </c>
       <c r="J38" s="0">
         <v>221.1927</v>
@@ -3662,7 +3662,7 @@
         <v>83</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>596</v>
+        <v>278</v>
       </c>
       <c r="J39" s="0">
         <v>210.51859999999999</v>
@@ -3694,7 +3694,7 @@
         <v>84</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>597</v>
+        <v>279</v>
       </c>
       <c r="J40" s="0">
         <v>368.1456</v>
@@ -3726,7 +3726,7 @@
         <v>85</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>598</v>
+        <v>280</v>
       </c>
       <c r="J41" s="0">
         <v>327.98309999999998</v>
@@ -3758,7 +3758,7 @@
         <v>86</v>
       </c>
       <c r="I42" s="0" t="s">
-        <v>599</v>
+        <v>281</v>
       </c>
       <c r="J42" s="0">
         <v>320.38529999999997</v>
@@ -3790,7 +3790,7 @@
         <v>87</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>600</v>
+        <v>282</v>
       </c>
       <c r="J43" s="0">
         <v>302.7507</v>
@@ -3822,7 +3822,7 @@
         <v>88</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>601</v>
+        <v>283</v>
       </c>
       <c r="J44" s="0">
         <v>278.7724</v>
@@ -3854,7 +3854,7 @@
         <v>89</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>602</v>
+        <v>284</v>
       </c>
       <c r="J45" s="0">
         <v>275.02319999999997</v>
@@ -3886,7 +3886,7 @@
         <v>90</v>
       </c>
       <c r="I46" s="0" t="s">
-        <v>603</v>
+        <v>285</v>
       </c>
       <c r="J46" s="0">
         <v>235.43600000000001</v>
@@ -3918,7 +3918,7 @@
         <v>91</v>
       </c>
       <c r="I47" s="0" t="s">
-        <v>604</v>
+        <v>286</v>
       </c>
       <c r="J47" s="0">
         <v>200.92150000000001</v>
@@ -3950,7 +3950,7 @@
         <v>92</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>605</v>
+        <v>287</v>
       </c>
       <c r="J48" s="0">
         <v>9411.1659999999993</v>
@@ -3982,7 +3982,7 @@
         <v>93</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>606</v>
+        <v>288</v>
       </c>
       <c r="J49" s="0">
         <v>9342.8192999999992</v>
@@ -4014,7 +4014,7 @@
         <v>94</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>607</v>
+        <v>289</v>
       </c>
       <c r="J50" s="0">
         <v>941.59280000000001</v>
@@ -4046,7 +4046,7 @@
         <v>95</v>
       </c>
       <c r="I51" s="0" t="s">
-        <v>608</v>
+        <v>290</v>
       </c>
       <c r="J51" s="0">
         <v>927.30880000000002</v>
@@ -4078,7 +4078,7 @@
         <v>96</v>
       </c>
       <c r="I52" s="0" t="s">
-        <v>609</v>
+        <v>291</v>
       </c>
       <c r="J52" s="0">
         <v>385.38529999999997</v>
@@ -4110,7 +4110,7 @@
         <v>97</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>610</v>
+        <v>292</v>
       </c>
       <c r="J53" s="0">
         <v>329.19709999999998</v>
@@ -4142,7 +4142,7 @@
         <v>98</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>611</v>
+        <v>293</v>
       </c>
       <c r="J54" s="0">
         <v>234.09270000000001</v>
@@ -4174,7 +4174,7 @@
         <v>99</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>612</v>
+        <v>294</v>
       </c>
       <c r="J55" s="0">
         <v>208.97069999999999</v>
@@ -4206,7 +4206,7 @@
         <v>100</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>613</v>
+        <v>295</v>
       </c>
       <c r="J56" s="0">
         <v>306.70839999999998</v>
@@ -4238,7 +4238,7 @@
         <v>101</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>614</v>
+        <v>296</v>
       </c>
       <c r="J57" s="0">
         <v>296.32659999999999</v>
@@ -4270,7 +4270,7 @@
         <v>102</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>615</v>
+        <v>297</v>
       </c>
       <c r="J58" s="0">
         <v>294.18619999999999</v>
@@ -4302,7 +4302,7 @@
         <v>103</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>616</v>
+        <v>298</v>
       </c>
       <c r="J59" s="0">
         <v>293.80200000000002</v>
@@ -4334,7 +4334,7 @@
         <v>104</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>617</v>
+        <v>299</v>
       </c>
       <c r="J60" s="0">
         <v>15461.819299999999</v>
@@ -4366,7 +4366,7 @@
         <v>105</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>618</v>
+        <v>300</v>
       </c>
       <c r="J61" s="0">
         <v>10367.752</v>
@@ -4398,7 +4398,7 @@
         <v>106</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>619</v>
+        <v>301</v>
       </c>
       <c r="J62" s="0">
         <v>1905.2927</v>
@@ -4430,7 +4430,7 @@
         <v>107</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>620</v>
+        <v>302</v>
       </c>
       <c r="J63" s="0">
         <v>975.92460000000005</v>
@@ -4462,7 +4462,7 @@
         <v>108</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>621</v>
+        <v>303</v>
       </c>
       <c r="J64" s="0">
         <v>581.38819999999998</v>
@@ -4494,7 +4494,7 @@
         <v>109</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>622</v>
+        <v>304</v>
       </c>
       <c r="J65" s="0">
         <v>546.27200000000005</v>
@@ -4526,7 +4526,7 @@
         <v>110</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>623</v>
+        <v>305</v>
       </c>
       <c r="J66" s="0">
         <v>536.43460000000005</v>
@@ -4558,7 +4558,7 @@
         <v>111</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>624</v>
+        <v>306</v>
       </c>
       <c r="J67" s="0">
         <v>533.26229999999998</v>
@@ -4590,7 +4590,7 @@
         <v>112</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>625</v>
+        <v>307</v>
       </c>
       <c r="J68" s="0">
         <v>523.20399999999995</v>
@@ -4622,7 +4622,7 @@
         <v>113</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>626</v>
+        <v>308</v>
       </c>
       <c r="J69" s="0">
         <v>516.61569999999995</v>
@@ -4654,7 +4654,7 @@
         <v>114</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>627</v>
+        <v>309</v>
       </c>
       <c r="J70" s="0">
         <v>479.05590000000001</v>
@@ -4686,7 +4686,7 @@
         <v>115</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>628</v>
+        <v>310</v>
       </c>
       <c r="J71" s="0">
         <v>442.88510000000002</v>
@@ -4718,7 +4718,7 @@
         <v>116</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>629</v>
+        <v>311</v>
       </c>
       <c r="J72" s="0">
         <v>384.4887</v>
@@ -4750,7 +4750,7 @@
         <v>117</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>630</v>
+        <v>312</v>
       </c>
       <c r="J73" s="0">
         <v>341.47399999999999</v>
@@ -4782,7 +4782,7 @@
         <v>118</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>631</v>
+        <v>313</v>
       </c>
       <c r="J74" s="0">
         <v>292.89060000000001</v>
@@ -4814,7 +4814,7 @@
         <v>119</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>632</v>
+        <v>314</v>
       </c>
       <c r="J75" s="0">
         <v>292.57459999999998</v>
@@ -4846,7 +4846,7 @@
         <v>120</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>633</v>
+        <v>315</v>
       </c>
       <c r="J76" s="0">
         <v>284.52800000000002</v>
@@ -4878,7 +4878,7 @@
         <v>61</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>634</v>
+        <v>316</v>
       </c>
       <c r="J77" s="0">
         <v>284.25450000000001</v>
@@ -4910,7 +4910,7 @@
         <v>121</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>635</v>
+        <v>317</v>
       </c>
       <c r="J78" s="0">
         <v>279.87459999999999</v>
@@ -4942,7 +4942,7 @@
         <v>122</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>636</v>
+        <v>318</v>
       </c>
       <c r="J79" s="0">
         <v>268.24270000000001</v>
@@ -4974,7 +4974,7 @@
         <v>443</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>637</v>
+        <v>529</v>
       </c>
       <c r="J80" s="0">
         <v>10499.483399999999</v>
@@ -5006,7 +5006,7 @@
         <v>444</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>638</v>
+        <v>530</v>
       </c>
       <c r="J81" s="0">
         <v>9639.3300999999992</v>
@@ -5038,7 +5038,7 @@
         <v>447</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>639</v>
+        <v>533</v>
       </c>
       <c r="J82" s="0">
         <v>388.74549999999999</v>
@@ -5070,7 +5070,7 @@
         <v>448</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>640</v>
+        <v>534</v>
       </c>
       <c r="J83" s="0">
         <v>308.16899999999998</v>
@@ -5102,7 +5102,7 @@
         <v>449</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>641</v>
+        <v>535</v>
       </c>
       <c r="J84" s="0">
         <v>305.76100000000002</v>
@@ -5134,7 +5134,7 @@
         <v>451</v>
       </c>
       <c r="I85" s="0" t="s">
-        <v>642</v>
+        <v>537</v>
       </c>
       <c r="J85" s="0">
         <v>297.43759999999998</v>
@@ -5166,7 +5166,7 @@
         <v>452</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>643</v>
+        <v>538</v>
       </c>
       <c r="J86" s="0">
         <v>283.1619</v>
@@ -5198,7 +5198,7 @@
         <v>453</v>
       </c>
       <c r="I87" s="0" t="s">
-        <v>644</v>
+        <v>539</v>
       </c>
       <c r="J87" s="0">
         <v>247.529</v>
@@ -5230,7 +5230,7 @@
         <v>454</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>645</v>
+        <v>540</v>
       </c>
       <c r="J88" s="0">
         <v>231.5712</v>
@@ -5262,7 +5262,7 @@
         <v>455</v>
       </c>
       <c r="I89" s="0" t="s">
-        <v>646</v>
+        <v>541</v>
       </c>
       <c r="J89" s="0">
         <v>1517.5046</v>
@@ -5294,7 +5294,7 @@
         <v>456</v>
       </c>
       <c r="I90" s="0" t="s">
-        <v>647</v>
+        <v>542</v>
       </c>
       <c r="J90" s="0">
         <v>1414.645</v>
@@ -5326,7 +5326,7 @@
         <v>457</v>
       </c>
       <c r="I91" s="0" t="s">
-        <v>648</v>
+        <v>543</v>
       </c>
       <c r="J91" s="0">
         <v>385.28089999999998</v>
@@ -5358,7 +5358,7 @@
         <v>458</v>
       </c>
       <c r="I92" s="0" t="s">
-        <v>649</v>
+        <v>544</v>
       </c>
       <c r="J92" s="0">
         <v>310.61110000000002</v>
@@ -5390,7 +5390,7 @@
         <v>459</v>
       </c>
       <c r="I93" s="0" t="s">
-        <v>650</v>
+        <v>545</v>
       </c>
       <c r="J93" s="0">
         <v>277.84199999999999</v>
@@ -5422,7 +5422,7 @@
         <v>63</v>
       </c>
       <c r="I94" s="0" t="s">
-        <v>651</v>
+        <v>546</v>
       </c>
       <c r="J94" s="0">
         <v>223.45169999999999</v>
@@ -5454,7 +5454,7 @@
         <v>460</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>652</v>
+        <v>547</v>
       </c>
       <c r="J95" s="0">
         <v>10215.762699999999</v>
@@ -5486,7 +5486,7 @@
         <v>461</v>
       </c>
       <c r="I96" s="0" t="s">
-        <v>653</v>
+        <v>548</v>
       </c>
       <c r="J96" s="0">
         <v>8851.0136999999995</v>
@@ -5518,7 +5518,7 @@
         <v>462</v>
       </c>
       <c r="I97" s="0" t="s">
-        <v>654</v>
+        <v>549</v>
       </c>
       <c r="J97" s="0">
         <v>1106.4232</v>
@@ -5550,7 +5550,7 @@
         <v>463</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>655</v>
+        <v>550</v>
       </c>
       <c r="J98" s="0">
         <v>909.94200000000001</v>
@@ -5582,7 +5582,7 @@
         <v>464</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>656</v>
+        <v>551</v>
       </c>
       <c r="J99" s="0">
         <v>316.77910000000003</v>
@@ -5614,7 +5614,7 @@
         <v>465</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>657</v>
+        <v>552</v>
       </c>
       <c r="J100" s="0">
         <v>284.43700000000001</v>
@@ -5646,7 +5646,7 @@
         <v>466</v>
       </c>
       <c r="I101" s="0" t="s">
-        <v>658</v>
+        <v>553</v>
       </c>
       <c r="J101" s="0">
         <v>282.07659999999999</v>
@@ -5678,7 +5678,7 @@
         <v>467</v>
       </c>
       <c r="I102" s="0" t="s">
-        <v>659</v>
+        <v>554</v>
       </c>
       <c r="J102" s="0">
         <v>261.52760000000001</v>
@@ -5710,7 +5710,7 @@
         <v>468</v>
       </c>
       <c r="I103" s="0" t="s">
-        <v>660</v>
+        <v>555</v>
       </c>
       <c r="J103" s="0">
         <v>248.01570000000001</v>
@@ -5742,7 +5742,7 @@
         <v>469</v>
       </c>
       <c r="I104" s="0" t="s">
-        <v>661</v>
+        <v>556</v>
       </c>
       <c r="J104" s="0">
         <v>246.53380000000001</v>
@@ -5774,7 +5774,7 @@
         <v>470</v>
       </c>
       <c r="I105" s="0" t="s">
-        <v>662</v>
+        <v>557</v>
       </c>
       <c r="J105" s="0">
         <v>228.9768</v>
@@ -5806,7 +5806,7 @@
         <v>471</v>
       </c>
       <c r="I106" s="0" t="s">
-        <v>663</v>
+        <v>558</v>
       </c>
       <c r="J106" s="0">
         <v>216.21680000000001</v>
@@ -5838,7 +5838,7 @@
         <v>123</v>
       </c>
       <c r="I107" s="0" t="s">
-        <v>664</v>
+        <v>319</v>
       </c>
       <c r="J107" s="0">
         <v>10261.8174</v>
@@ -5870,7 +5870,7 @@
         <v>124</v>
       </c>
       <c r="I108" s="0" t="s">
-        <v>665</v>
+        <v>320</v>
       </c>
       <c r="J108" s="0">
         <v>9826.5293000000001</v>
@@ -5902,7 +5902,7 @@
         <v>125</v>
       </c>
       <c r="I109" s="0" t="s">
-        <v>666</v>
+        <v>321</v>
       </c>
       <c r="J109" s="0">
         <v>310.85700000000003</v>
@@ -5934,7 +5934,7 @@
         <v>126</v>
       </c>
       <c r="I110" s="0" t="s">
-        <v>667</v>
+        <v>322</v>
       </c>
       <c r="J110" s="0">
         <v>294.82119999999998</v>
@@ -5966,7 +5966,7 @@
         <v>127</v>
       </c>
       <c r="I111" s="0" t="s">
-        <v>668</v>
+        <v>323</v>
       </c>
       <c r="J111" s="0">
         <v>290.76960000000003</v>
@@ -5998,7 +5998,7 @@
         <v>128</v>
       </c>
       <c r="I112" s="0" t="s">
-        <v>669</v>
+        <v>324</v>
       </c>
       <c r="J112" s="0">
         <v>273.49590000000001</v>
@@ -6030,7 +6030,7 @@
         <v>129</v>
       </c>
       <c r="I113" s="0" t="s">
-        <v>670</v>
+        <v>325</v>
       </c>
       <c r="J113" s="0">
         <v>242.22909999999999</v>
@@ -6062,7 +6062,7 @@
         <v>130</v>
       </c>
       <c r="I114" s="0" t="s">
-        <v>671</v>
+        <v>326</v>
       </c>
       <c r="J114" s="0">
         <v>238.70050000000001</v>
@@ -6094,7 +6094,7 @@
         <v>131</v>
       </c>
       <c r="I115" s="0" t="s">
-        <v>672</v>
+        <v>327</v>
       </c>
       <c r="J115" s="0">
         <v>227.2551</v>
@@ -6126,7 +6126,7 @@
         <v>132</v>
       </c>
       <c r="I116" s="0" t="s">
-        <v>673</v>
+        <v>328</v>
       </c>
       <c r="J116" s="0">
         <v>214.56540000000001</v>
@@ -6158,7 +6158,7 @@
         <v>133</v>
       </c>
       <c r="I117" s="0" t="s">
-        <v>674</v>
+        <v>329</v>
       </c>
       <c r="J117" s="0">
         <v>9905.6357000000007</v>
@@ -6190,7 +6190,7 @@
         <v>134</v>
       </c>
       <c r="I118" s="0" t="s">
-        <v>675</v>
+        <v>330</v>
       </c>
       <c r="J118" s="0">
         <v>8499.6309000000001</v>
@@ -6222,7 +6222,7 @@
         <v>135</v>
       </c>
       <c r="I119" s="0" t="s">
-        <v>676</v>
+        <v>331</v>
       </c>
       <c r="J119" s="0">
         <v>1404.5636</v>
@@ -6254,7 +6254,7 @@
         <v>136</v>
       </c>
       <c r="I120" s="0" t="s">
-        <v>677</v>
+        <v>332</v>
       </c>
       <c r="J120" s="0">
         <v>315.27960000000002</v>
@@ -6286,7 +6286,7 @@
         <v>137</v>
       </c>
       <c r="I121" s="0" t="s">
-        <v>678</v>
+        <v>333</v>
       </c>
       <c r="J121" s="0">
         <v>302.22129999999999</v>
@@ -6318,7 +6318,7 @@
         <v>138</v>
       </c>
       <c r="I122" s="0" t="s">
-        <v>679</v>
+        <v>334</v>
       </c>
       <c r="J122" s="0">
         <v>266.9862</v>
@@ -6350,7 +6350,7 @@
         <v>139</v>
       </c>
       <c r="I123" s="0" t="s">
-        <v>680</v>
+        <v>335</v>
       </c>
       <c r="J123" s="0">
         <v>264.11059999999998</v>
@@ -6382,7 +6382,7 @@
         <v>140</v>
       </c>
       <c r="I124" s="0" t="s">
-        <v>681</v>
+        <v>336</v>
       </c>
       <c r="J124" s="0">
         <v>247.79859999999999</v>
@@ -6414,7 +6414,7 @@
         <v>141</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>682</v>
+        <v>337</v>
       </c>
       <c r="J125" s="0">
         <v>239.36019999999999</v>
@@ -6446,7 +6446,7 @@
         <v>142</v>
       </c>
       <c r="I126" s="0" t="s">
-        <v>683</v>
+        <v>338</v>
       </c>
       <c r="J126" s="0">
         <v>208.72989999999999</v>
@@ -6478,7 +6478,7 @@
         <v>143</v>
       </c>
       <c r="I127" s="0" t="s">
-        <v>684</v>
+        <v>339</v>
       </c>
       <c r="J127" s="0">
         <v>199.44909999999999</v>
@@ -6510,7 +6510,7 @@
         <v>144</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>685</v>
+        <v>340</v>
       </c>
       <c r="J128" s="0">
         <v>9596.9883000000009</v>
@@ -6542,7 +6542,7 @@
         <v>145</v>
       </c>
       <c r="I129" s="0" t="s">
-        <v>686</v>
+        <v>341</v>
       </c>
       <c r="J129" s="0">
         <v>8798.1787000000004</v>
@@ -6574,7 +6574,7 @@
         <v>146</v>
       </c>
       <c r="I130" s="0" t="s">
-        <v>687</v>
+        <v>342</v>
       </c>
       <c r="J130" s="0">
         <v>1321.1365000000001</v>
@@ -6606,7 +6606,7 @@
         <v>147</v>
       </c>
       <c r="I131" s="0" t="s">
-        <v>688</v>
+        <v>343</v>
       </c>
       <c r="J131" s="0">
         <v>959.9144</v>
@@ -6638,7 +6638,7 @@
         <v>148</v>
       </c>
       <c r="I132" s="0" t="s">
-        <v>689</v>
+        <v>344</v>
       </c>
       <c r="J132" s="0">
         <v>309.23169999999999</v>
@@ -6670,7 +6670,7 @@
         <v>149</v>
       </c>
       <c r="I133" s="0" t="s">
-        <v>690</v>
+        <v>345</v>
       </c>
       <c r="J133" s="0">
         <v>301.12470000000002</v>
@@ -6702,7 +6702,7 @@
         <v>150</v>
       </c>
       <c r="I134" s="0" t="s">
-        <v>691</v>
+        <v>346</v>
       </c>
       <c r="J134" s="0">
         <v>296.84010000000001</v>
@@ -6734,7 +6734,7 @@
         <v>151</v>
       </c>
       <c r="I135" s="0" t="s">
-        <v>692</v>
+        <v>347</v>
       </c>
       <c r="J135" s="0">
         <v>288.2115</v>
@@ -6766,7 +6766,7 @@
         <v>152</v>
       </c>
       <c r="I136" s="0" t="s">
-        <v>693</v>
+        <v>348</v>
       </c>
       <c r="J136" s="0">
         <v>274.3639</v>
@@ -6798,7 +6798,7 @@
         <v>153</v>
       </c>
       <c r="I137" s="0" t="s">
-        <v>694</v>
+        <v>349</v>
       </c>
       <c r="J137" s="0">
         <v>260.00229999999999</v>
@@ -6830,7 +6830,7 @@
         <v>154</v>
       </c>
       <c r="I138" s="0" t="s">
-        <v>695</v>
+        <v>350</v>
       </c>
       <c r="J138" s="0">
         <v>246.21190000000001</v>
@@ -6862,7 +6862,7 @@
         <v>155</v>
       </c>
       <c r="I139" s="0" t="s">
-        <v>696</v>
+        <v>351</v>
       </c>
       <c r="J139" s="0">
         <v>180.47190000000001</v>
@@ -6894,7 +6894,7 @@
         <v>156</v>
       </c>
       <c r="I140" s="0" t="s">
-        <v>697</v>
+        <v>352</v>
       </c>
       <c r="J140" s="0">
         <v>9836.6807000000008</v>
@@ -6926,7 +6926,7 @@
         <v>158</v>
       </c>
       <c r="I141" s="0" t="s">
-        <v>698</v>
+        <v>354</v>
       </c>
       <c r="J141" s="0">
         <v>908.87840000000006</v>
@@ -6958,7 +6958,7 @@
         <v>159</v>
       </c>
       <c r="I142" s="0" t="s">
-        <v>699</v>
+        <v>355</v>
       </c>
       <c r="J142" s="0">
         <v>840.46699999999999</v>
@@ -6990,7 +6990,7 @@
         <v>160</v>
       </c>
       <c r="I143" s="0" t="s">
-        <v>700</v>
+        <v>356</v>
       </c>
       <c r="J143" s="0">
         <v>385.22919999999999</v>
@@ -7022,7 +7022,7 @@
         <v>161</v>
       </c>
       <c r="I144" s="0" t="s">
-        <v>701</v>
+        <v>357</v>
       </c>
       <c r="J144" s="0">
         <v>310.47890000000001</v>
@@ -7054,7 +7054,7 @@
         <v>162</v>
       </c>
       <c r="I145" s="0" t="s">
-        <v>702</v>
+        <v>358</v>
       </c>
       <c r="J145" s="0">
         <v>300.91699999999997</v>
@@ -7086,7 +7086,7 @@
         <v>163</v>
       </c>
       <c r="I146" s="0" t="s">
-        <v>703</v>
+        <v>359</v>
       </c>
       <c r="J146" s="0">
         <v>285.7113</v>
@@ -7118,7 +7118,7 @@
         <v>164</v>
       </c>
       <c r="I147" s="0" t="s">
-        <v>704</v>
+        <v>360</v>
       </c>
       <c r="J147" s="0">
         <v>255.1182</v>
@@ -7150,7 +7150,7 @@
         <v>165</v>
       </c>
       <c r="I148" s="0" t="s">
-        <v>705</v>
+        <v>361</v>
       </c>
       <c r="J148" s="0">
         <v>251.63229999999999</v>
@@ -7182,7 +7182,7 @@
         <v>166</v>
       </c>
       <c r="I149" s="0" t="s">
-        <v>706</v>
+        <v>362</v>
       </c>
       <c r="J149" s="0">
         <v>241.47989999999999</v>
@@ -7214,7 +7214,7 @@
         <v>167</v>
       </c>
       <c r="I150" s="0" t="s">
-        <v>707</v>
+        <v>363</v>
       </c>
       <c r="J150" s="0">
         <v>239.88820000000001</v>
@@ -7246,7 +7246,7 @@
         <v>168</v>
       </c>
       <c r="I151" s="0" t="s">
-        <v>708</v>
+        <v>364</v>
       </c>
       <c r="J151" s="0">
         <v>10661.891600000001</v>
@@ -7278,7 +7278,7 @@
         <v>169</v>
       </c>
       <c r="I152" s="0" t="s">
-        <v>709</v>
+        <v>365</v>
       </c>
       <c r="J152" s="0">
         <v>7643.7520000000004</v>
@@ -7310,7 +7310,7 @@
         <v>170</v>
       </c>
       <c r="I153" s="0" t="s">
-        <v>710</v>
+        <v>366</v>
       </c>
       <c r="J153" s="0">
         <v>1539.2754</v>
@@ -7342,7 +7342,7 @@
         <v>171</v>
       </c>
       <c r="I154" s="0" t="s">
-        <v>711</v>
+        <v>367</v>
       </c>
       <c r="J154" s="0">
         <v>1393.9193</v>
@@ -7374,7 +7374,7 @@
         <v>172</v>
       </c>
       <c r="I155" s="0" t="s">
-        <v>712</v>
+        <v>368</v>
       </c>
       <c r="J155" s="0">
         <v>457.66739999999999</v>
@@ -7406,7 +7406,7 @@
         <v>173</v>
       </c>
       <c r="I156" s="0" t="s">
-        <v>713</v>
+        <v>369</v>
       </c>
       <c r="J156" s="0">
         <v>419.16669999999999</v>
@@ -7438,7 +7438,7 @@
         <v>174</v>
       </c>
       <c r="I157" s="0" t="s">
-        <v>714</v>
+        <v>370</v>
       </c>
       <c r="J157" s="0">
         <v>417.49169999999998</v>
@@ -7470,7 +7470,7 @@
         <v>175</v>
       </c>
       <c r="I158" s="0" t="s">
-        <v>715</v>
+        <v>371</v>
       </c>
       <c r="J158" s="0">
         <v>399.00799999999998</v>
@@ -7502,7 +7502,7 @@
         <v>176</v>
       </c>
       <c r="I159" s="0" t="s">
-        <v>716</v>
+        <v>372</v>
       </c>
       <c r="J159" s="0">
         <v>361.1662</v>
@@ -7534,7 +7534,7 @@
         <v>178</v>
       </c>
       <c r="I160" s="0" t="s">
-        <v>717</v>
+        <v>374</v>
       </c>
       <c r="J160" s="0">
         <v>311.19600000000003</v>
@@ -7566,7 +7566,7 @@
         <v>179</v>
       </c>
       <c r="I161" s="0" t="s">
-        <v>718</v>
+        <v>375</v>
       </c>
       <c r="J161" s="0">
         <v>291.23480000000001</v>
@@ -7598,7 +7598,7 @@
         <v>180</v>
       </c>
       <c r="I162" s="0" t="s">
-        <v>719</v>
+        <v>376</v>
       </c>
       <c r="J162" s="0">
         <v>9127.5985999999994</v>
@@ -7630,7 +7630,7 @@
         <v>181</v>
       </c>
       <c r="I163" s="0" t="s">
-        <v>720</v>
+        <v>377</v>
       </c>
       <c r="J163" s="0">
         <v>8554.8642999999993</v>
@@ -7662,7 +7662,7 @@
         <v>182</v>
       </c>
       <c r="I164" s="0" t="s">
-        <v>721</v>
+        <v>378</v>
       </c>
       <c r="J164" s="0">
         <v>1414.848</v>
@@ -7694,7 +7694,7 @@
         <v>183</v>
       </c>
       <c r="I165" s="0" t="s">
-        <v>722</v>
+        <v>379</v>
       </c>
       <c r="J165" s="0">
         <v>752.67660000000001</v>
@@ -7726,7 +7726,7 @@
         <v>184</v>
       </c>
       <c r="I166" s="0" t="s">
-        <v>723</v>
+        <v>380</v>
       </c>
       <c r="J166" s="0">
         <v>348.73090000000002</v>
@@ -7758,7 +7758,7 @@
         <v>185</v>
       </c>
       <c r="I167" s="0" t="s">
-        <v>724</v>
+        <v>381</v>
       </c>
       <c r="J167" s="0">
         <v>307.04939999999999</v>
@@ -7790,7 +7790,7 @@
         <v>186</v>
       </c>
       <c r="I168" s="0" t="s">
-        <v>725</v>
+        <v>382</v>
       </c>
       <c r="J168" s="0">
         <v>280.97919999999999</v>
@@ -7822,7 +7822,7 @@
         <v>187</v>
       </c>
       <c r="I169" s="0" t="s">
-        <v>726</v>
+        <v>383</v>
       </c>
       <c r="J169" s="0">
         <v>265.1284</v>
@@ -7854,7 +7854,7 @@
         <v>188</v>
       </c>
       <c r="I170" s="0" t="s">
-        <v>727</v>
+        <v>384</v>
       </c>
       <c r="J170" s="0">
         <v>249.8895</v>
@@ -7886,7 +7886,7 @@
         <v>189</v>
       </c>
       <c r="I171" s="0" t="s">
-        <v>728</v>
+        <v>385</v>
       </c>
       <c r="J171" s="0">
         <v>215.3955</v>
@@ -7918,7 +7918,7 @@
         <v>190</v>
       </c>
       <c r="I172" s="0" t="s">
-        <v>729</v>
+        <v>386</v>
       </c>
       <c r="J172" s="0">
         <v>213.6302</v>
@@ -7950,7 +7950,7 @@
         <v>191</v>
       </c>
       <c r="I173" s="0" t="s">
-        <v>730</v>
+        <v>387</v>
       </c>
       <c r="J173" s="0">
         <v>193.54920000000001</v>
@@ -7982,7 +7982,7 @@
         <v>192</v>
       </c>
       <c r="I174" s="0" t="s">
-        <v>731</v>
+        <v>388</v>
       </c>
       <c r="J174" s="0">
         <v>9254.9814000000006</v>
@@ -8014,7 +8014,7 @@
         <v>193</v>
       </c>
       <c r="I175" s="0" t="s">
-        <v>732</v>
+        <v>389</v>
       </c>
       <c r="J175" s="0">
         <v>8396.3974999999991</v>
@@ -8046,7 +8046,7 @@
         <v>194</v>
       </c>
       <c r="I176" s="0" t="s">
-        <v>733</v>
+        <v>390</v>
       </c>
       <c r="J176" s="0">
         <v>1087.1931999999999</v>
@@ -8078,7 +8078,7 @@
         <v>195</v>
       </c>
       <c r="I177" s="0" t="s">
-        <v>734</v>
+        <v>391</v>
       </c>
       <c r="J177" s="0">
         <v>1026.0048999999999</v>
@@ -8110,7 +8110,7 @@
         <v>196</v>
       </c>
       <c r="I178" s="0" t="s">
-        <v>735</v>
+        <v>392</v>
       </c>
       <c r="J178" s="0">
         <v>328.2697</v>
@@ -8142,7 +8142,7 @@
         <v>197</v>
       </c>
       <c r="I179" s="0" t="s">
-        <v>736</v>
+        <v>393</v>
       </c>
       <c r="J179" s="0">
         <v>306.13749999999999</v>
@@ -8174,7 +8174,7 @@
         <v>198</v>
       </c>
       <c r="I180" s="0" t="s">
-        <v>737</v>
+        <v>394</v>
       </c>
       <c r="J180" s="0">
         <v>302.69369999999998</v>
@@ -8206,7 +8206,7 @@
         <v>199</v>
       </c>
       <c r="I181" s="0" t="s">
-        <v>738</v>
+        <v>395</v>
       </c>
       <c r="J181" s="0">
         <v>296.63529999999997</v>
@@ -8238,7 +8238,7 @@
         <v>200</v>
       </c>
       <c r="I182" s="0" t="s">
-        <v>739</v>
+        <v>396</v>
       </c>
       <c r="J182" s="0">
         <v>292.96969999999999</v>
@@ -8270,7 +8270,7 @@
         <v>201</v>
       </c>
       <c r="I183" s="0" t="s">
-        <v>740</v>
+        <v>397</v>
       </c>
       <c r="J183" s="0">
         <v>267.35629999999998</v>
@@ -8302,7 +8302,7 @@
         <v>203</v>
       </c>
       <c r="I184" s="0" t="s">
-        <v>741</v>
+        <v>399</v>
       </c>
       <c r="J184" s="0">
         <v>165.21969999999999</v>
@@ -8334,7 +8334,7 @@
         <v>206</v>
       </c>
       <c r="I185" s="0" t="s">
-        <v>742</v>
+        <v>402</v>
       </c>
       <c r="J185" s="0">
         <v>1713.3430000000001</v>
@@ -8366,7 +8366,7 @@
         <v>207</v>
       </c>
       <c r="I186" s="0" t="s">
-        <v>743</v>
+        <v>403</v>
       </c>
       <c r="J186" s="0">
         <v>1254.9603</v>
@@ -8398,7 +8398,7 @@
         <v>208</v>
       </c>
       <c r="I187" s="0" t="s">
-        <v>744</v>
+        <v>404</v>
       </c>
       <c r="J187" s="0">
         <v>412.1336</v>
@@ -8430,7 +8430,7 @@
         <v>209</v>
       </c>
       <c r="I188" s="0" t="s">
-        <v>745</v>
+        <v>405</v>
       </c>
       <c r="J188" s="0">
         <v>395.3304</v>
@@ -8462,7 +8462,7 @@
         <v>210</v>
       </c>
       <c r="I189" s="0" t="s">
-        <v>746</v>
+        <v>406</v>
       </c>
       <c r="J189" s="0">
         <v>314.40159999999997</v>
@@ -8494,7 +8494,7 @@
         <v>211</v>
       </c>
       <c r="I190" s="0" t="s">
-        <v>747</v>
+        <v>407</v>
       </c>
       <c r="J190" s="0">
         <v>306.70960000000002</v>
@@ -8526,7 +8526,7 @@
         <v>212</v>
       </c>
       <c r="I191" s="0" t="s">
-        <v>748</v>
+        <v>408</v>
       </c>
       <c r="J191" s="0">
         <v>285.86070000000001</v>
@@ -8558,7 +8558,7 @@
         <v>213</v>
       </c>
       <c r="I192" s="0" t="s">
-        <v>749</v>
+        <v>409</v>
       </c>
       <c r="J192" s="0">
         <v>284.4486</v>
@@ -8590,7 +8590,7 @@
         <v>214</v>
       </c>
       <c r="I193" s="0" t="s">
-        <v>750</v>
+        <v>410</v>
       </c>
       <c r="J193" s="0">
         <v>281.97449999999998</v>
@@ -8622,7 +8622,7 @@
         <v>216</v>
       </c>
       <c r="I194" s="0" t="s">
-        <v>751</v>
+        <v>412</v>
       </c>
       <c r="J194" s="0">
         <v>9423.6895000000004</v>
@@ -8654,7 +8654,7 @@
         <v>217</v>
       </c>
       <c r="I195" s="0" t="s">
-        <v>752</v>
+        <v>413</v>
       </c>
       <c r="J195" s="0">
         <v>9234.3525000000009</v>
@@ -8686,7 +8686,7 @@
         <v>218</v>
       </c>
       <c r="I196" s="0" t="s">
-        <v>753</v>
+        <v>414</v>
       </c>
       <c r="J196" s="0">
         <v>1208.9946</v>
@@ -8718,7 +8718,7 @@
         <v>219</v>
       </c>
       <c r="I197" s="0" t="s">
-        <v>754</v>
+        <v>415</v>
       </c>
       <c r="J197" s="0">
         <v>951.19749999999999</v>
@@ -8750,7 +8750,7 @@
         <v>220</v>
       </c>
       <c r="I198" s="0" t="s">
-        <v>755</v>
+        <v>416</v>
       </c>
       <c r="J198" s="0">
         <v>316.12619999999998</v>
@@ -8782,7 +8782,7 @@
         <v>221</v>
       </c>
       <c r="I199" s="0" t="s">
-        <v>756</v>
+        <v>417</v>
       </c>
       <c r="J199" s="0">
         <v>302.2124</v>
@@ -8814,7 +8814,7 @@
         <v>222</v>
       </c>
       <c r="I200" s="0" t="s">
-        <v>757</v>
+        <v>418</v>
       </c>
       <c r="J200" s="0">
         <v>294.96859999999998</v>
@@ -8846,7 +8846,7 @@
         <v>223</v>
       </c>
       <c r="I201" s="0" t="s">
-        <v>758</v>
+        <v>419</v>
       </c>
       <c r="J201" s="0">
         <v>291.27109999999999</v>
@@ -8878,7 +8878,7 @@
         <v>224</v>
       </c>
       <c r="I202" s="0" t="s">
-        <v>759</v>
+        <v>420</v>
       </c>
       <c r="J202" s="0">
         <v>264.68939999999998</v>
@@ -8910,7 +8910,7 @@
         <v>225</v>
       </c>
       <c r="I203" s="0" t="s">
-        <v>760</v>
+        <v>421</v>
       </c>
       <c r="J203" s="0">
         <v>257.6934</v>
@@ -8942,7 +8942,7 @@
         <v>226</v>
       </c>
       <c r="I204" s="0" t="s">
-        <v>761</v>
+        <v>422</v>
       </c>
       <c r="J204" s="0">
         <v>214.37610000000001</v>
@@ -8974,7 +8974,7 @@
         <v>227</v>
       </c>
       <c r="I205" s="0" t="s">
-        <v>762</v>
+        <v>423</v>
       </c>
       <c r="J205" s="0">
         <v>190.58150000000001</v>
@@ -9006,7 +9006,7 @@
         <v>228</v>
       </c>
       <c r="I206" s="0" t="s">
-        <v>763</v>
+        <v>424</v>
       </c>
       <c r="J206" s="0">
         <v>10441.448200000001</v>
@@ -9038,7 +9038,7 @@
         <v>229</v>
       </c>
       <c r="I207" s="0" t="s">
-        <v>764</v>
+        <v>425</v>
       </c>
       <c r="J207" s="0">
         <v>9728.8516</v>
@@ -9070,7 +9070,7 @@
         <v>230</v>
       </c>
       <c r="I208" s="0" t="s">
-        <v>765</v>
+        <v>426</v>
       </c>
       <c r="J208" s="0">
         <v>1533.4409000000001</v>
@@ -9102,7 +9102,7 @@
         <v>231</v>
       </c>
       <c r="I209" s="0" t="s">
-        <v>766</v>
+        <v>427</v>
       </c>
       <c r="J209" s="0">
         <v>1358.2428</v>
@@ -9134,7 +9134,7 @@
         <v>232</v>
       </c>
       <c r="I210" s="0" t="s">
-        <v>767</v>
+        <v>428</v>
       </c>
       <c r="J210" s="0">
         <v>452.1069</v>
@@ -9166,7 +9166,7 @@
         <v>233</v>
       </c>
       <c r="I211" s="0" t="s">
-        <v>768</v>
+        <v>429</v>
       </c>
       <c r="J211" s="0">
         <v>439.75790000000001</v>
@@ -9198,7 +9198,7 @@
         <v>234</v>
       </c>
       <c r="I212" s="0" t="s">
-        <v>769</v>
+        <v>430</v>
       </c>
       <c r="J212" s="0">
         <v>376.52229999999997</v>
@@ -9230,7 +9230,7 @@
         <v>235</v>
       </c>
       <c r="I213" s="0" t="s">
-        <v>770</v>
+        <v>431</v>
       </c>
       <c r="J213" s="0">
         <v>375.43979999999999</v>
@@ -9262,7 +9262,7 @@
         <v>236</v>
       </c>
       <c r="I214" s="0" t="s">
-        <v>771</v>
+        <v>432</v>
       </c>
       <c r="J214" s="0">
         <v>373.55439999999999</v>
@@ -9294,7 +9294,7 @@
         <v>237</v>
       </c>
       <c r="I215" s="0" t="s">
-        <v>772</v>
+        <v>433</v>
       </c>
       <c r="J215" s="0">
         <v>302.76659999999998</v>
@@ -9326,7 +9326,7 @@
         <v>238</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>773</v>
+        <v>434</v>
       </c>
       <c r="J216" s="0">
         <v>300.86579999999998</v>
@@ -9358,7 +9358,7 @@
         <v>472</v>
       </c>
       <c r="I217" s="0" t="s">
-        <v>774</v>
+        <v>514</v>
       </c>
       <c r="J217" s="0">
         <v>12892.7021</v>
@@ -9390,7 +9390,7 @@
         <v>473</v>
       </c>
       <c r="I218" s="0" t="s">
-        <v>775</v>
+        <v>515</v>
       </c>
       <c r="J218" s="0">
         <v>10694.238300000001</v>
@@ -9422,7 +9422,7 @@
         <v>474</v>
       </c>
       <c r="I219" s="0" t="s">
-        <v>776</v>
+        <v>516</v>
       </c>
       <c r="J219" s="0">
         <v>2047.9614999999999</v>
@@ -9454,7 +9454,7 @@
         <v>475</v>
       </c>
       <c r="I220" s="0" t="s">
-        <v>777</v>
+        <v>517</v>
       </c>
       <c r="J220" s="0">
         <v>910.678</v>
@@ -9486,7 +9486,7 @@
         <v>477</v>
       </c>
       <c r="I221" s="0" t="s">
-        <v>778</v>
+        <v>519</v>
       </c>
       <c r="J221" s="0">
         <v>568.2056</v>
@@ -9518,7 +9518,7 @@
         <v>479</v>
       </c>
       <c r="I222" s="0" t="s">
-        <v>779</v>
+        <v>521</v>
       </c>
       <c r="J222" s="0">
         <v>489.4178</v>
@@ -9550,7 +9550,7 @@
         <v>481</v>
       </c>
       <c r="I223" s="0" t="s">
-        <v>780</v>
+        <v>523</v>
       </c>
       <c r="J223" s="0">
         <v>370.15899999999999</v>
@@ -9582,7 +9582,7 @@
         <v>483</v>
       </c>
       <c r="I224" s="0" t="s">
-        <v>781</v>
+        <v>525</v>
       </c>
       <c r="J224" s="0">
         <v>340.95030000000003</v>

--- a/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="127944" uniqueCount="782">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="138029" uniqueCount="782">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="138029" uniqueCount="782">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="142063" uniqueCount="782">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="142063" uniqueCount="782">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="146097" uniqueCount="782">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="146097" uniqueCount="782">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="164250" uniqueCount="782">
   <si>
     <t>Year</t>
   </si>
@@ -2408,16 +2408,16 @@
   <dimension ref="A1:J238"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.08984375" customWidth="true"/>
-    <col min="2" max="2" width="6.54296875" customWidth="true"/>
-    <col min="3" max="3" width="10.36328125" customWidth="true"/>
-    <col min="4" max="4" width="17.36328125" customWidth="true"/>
-    <col min="5" max="5" width="11.81640625" customWidth="true"/>
-    <col min="6" max="6" width="11.90625" customWidth="true"/>
-    <col min="7" max="7" width="7.90625" customWidth="true"/>
-    <col min="8" max="8" width="36.26953125" customWidth="true"/>
-    <col min="9" max="9" width="168.54296875" customWidth="true"/>
-    <col min="10" max="10" width="10.453125" customWidth="true"/>
+    <col min="1" max="1" width="14.85546875" customWidth="true"/>
+    <col min="2" max="2" width="7" customWidth="true"/>
+    <col min="3" max="3" width="11.28515625" customWidth="true"/>
+    <col min="4" max="4" width="18.28515625" customWidth="true"/>
+    <col min="5" max="5" width="12.7109375" customWidth="true"/>
+    <col min="6" max="6" width="13" customWidth="true"/>
+    <col min="7" max="7" width="8.5703125" customWidth="true"/>
+    <col min="8" max="8" width="37.42578125" customWidth="true"/>
+    <col min="9" max="9" width="176.42578125" customWidth="true"/>
+    <col min="10" max="10" width="10.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="164250" uniqueCount="782">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="172318" uniqueCount="782">
   <si>
     <t>Year</t>
   </si>
@@ -2416,7 +2416,7 @@
     <col min="6" max="6" width="13" customWidth="true"/>
     <col min="7" max="7" width="8.5703125" customWidth="true"/>
     <col min="8" max="8" width="37.42578125" customWidth="true"/>
-    <col min="9" max="9" width="176.42578125" customWidth="true"/>
+    <col min="9" max="9" width="148" customWidth="true"/>
     <col min="10" max="10" width="10.7109375" customWidth="true"/>
   </cols>
   <sheetData>
@@ -2478,7 +2478,7 @@
         <v>46</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>241</v>
+        <v>559</v>
       </c>
       <c r="J2" s="0">
         <v>9347.0458999999992</v>
@@ -2510,7 +2510,7 @@
         <v>47</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>242</v>
+        <v>560</v>
       </c>
       <c r="J3" s="0">
         <v>9278.2314000000006</v>
@@ -2542,7 +2542,7 @@
         <v>48</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>243</v>
+        <v>561</v>
       </c>
       <c r="J4" s="0">
         <v>1582.4756</v>
@@ -2574,7 +2574,7 @@
         <v>49</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>244</v>
+        <v>562</v>
       </c>
       <c r="J5" s="0">
         <v>1241.5624</v>
@@ -2606,7 +2606,7 @@
         <v>50</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>245</v>
+        <v>563</v>
       </c>
       <c r="J6" s="0">
         <v>421.89870000000002</v>
@@ -2638,7 +2638,7 @@
         <v>51</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>246</v>
+        <v>564</v>
       </c>
       <c r="J7" s="0">
         <v>398.66129999999998</v>
@@ -2670,7 +2670,7 @@
         <v>52</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>247</v>
+        <v>565</v>
       </c>
       <c r="J8" s="0">
         <v>328.8254</v>
@@ -2702,7 +2702,7 @@
         <v>53</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>248</v>
+        <v>566</v>
       </c>
       <c r="J9" s="0">
         <v>313.2783</v>
@@ -2734,7 +2734,7 @@
         <v>54</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>249</v>
+        <v>567</v>
       </c>
       <c r="J10" s="0">
         <v>295.0641</v>
@@ -2766,7 +2766,7 @@
         <v>55</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>250</v>
+        <v>568</v>
       </c>
       <c r="J11" s="0">
         <v>294.86309999999998</v>
@@ -2798,7 +2798,7 @@
         <v>56</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>251</v>
+        <v>569</v>
       </c>
       <c r="J12" s="0">
         <v>281.74770000000001</v>
@@ -2830,7 +2830,7 @@
         <v>57</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>252</v>
+        <v>570</v>
       </c>
       <c r="J13" s="0">
         <v>274.15789999999998</v>
@@ -2862,7 +2862,7 @@
         <v>58</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>253</v>
+        <v>571</v>
       </c>
       <c r="J14" s="0">
         <v>370.1397</v>
@@ -2894,7 +2894,7 @@
         <v>59</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>254</v>
+        <v>572</v>
       </c>
       <c r="J15" s="0">
         <v>292.09550000000002</v>
@@ -2926,7 +2926,7 @@
         <v>60</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>255</v>
+        <v>573</v>
       </c>
       <c r="J16" s="0">
         <v>289.81389999999999</v>
@@ -2958,7 +2958,7 @@
         <v>61</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>256</v>
+        <v>574</v>
       </c>
       <c r="J17" s="0">
         <v>284.25450000000001</v>
@@ -2990,7 +2990,7 @@
         <v>62</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>257</v>
+        <v>575</v>
       </c>
       <c r="J18" s="0">
         <v>242.2781</v>
@@ -3022,7 +3022,7 @@
         <v>63</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>258</v>
+        <v>576</v>
       </c>
       <c r="J19" s="0">
         <v>223.45169999999999</v>
@@ -3054,7 +3054,7 @@
         <v>64</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>259</v>
+        <v>577</v>
       </c>
       <c r="J20" s="0">
         <v>199.1625</v>
@@ -3086,7 +3086,7 @@
         <v>65</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>260</v>
+        <v>578</v>
       </c>
       <c r="J21" s="0">
         <v>194.94929999999999</v>
@@ -3118,7 +3118,7 @@
         <v>66</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>261</v>
+        <v>579</v>
       </c>
       <c r="J22" s="0">
         <v>347.25940000000003</v>
@@ -3150,7 +3150,7 @@
         <v>67</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>262</v>
+        <v>580</v>
       </c>
       <c r="J23" s="0">
         <v>331.1694</v>
@@ -3182,7 +3182,7 @@
         <v>68</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>263</v>
+        <v>581</v>
       </c>
       <c r="J24" s="0">
         <v>321.93639999999999</v>
@@ -3214,7 +3214,7 @@
         <v>69</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>264</v>
+        <v>582</v>
       </c>
       <c r="J25" s="0">
         <v>277.89530000000002</v>
@@ -3246,7 +3246,7 @@
         <v>70</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>265</v>
+        <v>583</v>
       </c>
       <c r="J26" s="0">
         <v>276.74470000000002</v>
@@ -3278,7 +3278,7 @@
         <v>71</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>266</v>
+        <v>584</v>
       </c>
       <c r="J27" s="0">
         <v>268.73340000000002</v>
@@ -3310,7 +3310,7 @@
         <v>72</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>267</v>
+        <v>585</v>
       </c>
       <c r="J28" s="0">
         <v>267.4108</v>
@@ -3342,7 +3342,7 @@
         <v>73</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>268</v>
+        <v>586</v>
       </c>
       <c r="J29" s="0">
         <v>246.4597</v>
@@ -3374,7 +3374,7 @@
         <v>74</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>269</v>
+        <v>587</v>
       </c>
       <c r="J30" s="0">
         <v>9973.1728999999996</v>
@@ -3406,7 +3406,7 @@
         <v>75</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>270</v>
+        <v>588</v>
       </c>
       <c r="J31" s="0">
         <v>8216.1016</v>
@@ -3438,7 +3438,7 @@
         <v>76</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>271</v>
+        <v>589</v>
       </c>
       <c r="J32" s="0">
         <v>381.02080000000001</v>
@@ -3470,7 +3470,7 @@
         <v>77</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>272</v>
+        <v>590</v>
       </c>
       <c r="J33" s="0">
         <v>329.35809999999998</v>
@@ -3502,7 +3502,7 @@
         <v>78</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>273</v>
+        <v>591</v>
       </c>
       <c r="J34" s="0">
         <v>298.96679999999998</v>
@@ -3534,7 +3534,7 @@
         <v>79</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>274</v>
+        <v>592</v>
       </c>
       <c r="J35" s="0">
         <v>290.85469999999998</v>
@@ -3566,7 +3566,7 @@
         <v>80</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>275</v>
+        <v>593</v>
       </c>
       <c r="J36" s="0">
         <v>260.34840000000003</v>
@@ -3598,7 +3598,7 @@
         <v>81</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>276</v>
+        <v>594</v>
       </c>
       <c r="J37" s="0">
         <v>243.72470000000001</v>
@@ -3630,7 +3630,7 @@
         <v>82</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>277</v>
+        <v>595</v>
       </c>
       <c r="J38" s="0">
         <v>221.1927</v>
@@ -3662,7 +3662,7 @@
         <v>83</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>278</v>
+        <v>596</v>
       </c>
       <c r="J39" s="0">
         <v>210.51859999999999</v>
@@ -3694,7 +3694,7 @@
         <v>84</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>279</v>
+        <v>597</v>
       </c>
       <c r="J40" s="0">
         <v>368.1456</v>
@@ -3726,7 +3726,7 @@
         <v>85</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>280</v>
+        <v>598</v>
       </c>
       <c r="J41" s="0">
         <v>327.98309999999998</v>
@@ -3758,7 +3758,7 @@
         <v>86</v>
       </c>
       <c r="I42" s="0" t="s">
-        <v>281</v>
+        <v>599</v>
       </c>
       <c r="J42" s="0">
         <v>320.38529999999997</v>
@@ -3790,7 +3790,7 @@
         <v>87</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>282</v>
+        <v>600</v>
       </c>
       <c r="J43" s="0">
         <v>302.7507</v>
@@ -3822,7 +3822,7 @@
         <v>88</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>283</v>
+        <v>601</v>
       </c>
       <c r="J44" s="0">
         <v>278.7724</v>
@@ -3854,7 +3854,7 @@
         <v>89</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>284</v>
+        <v>602</v>
       </c>
       <c r="J45" s="0">
         <v>275.02319999999997</v>
@@ -3886,7 +3886,7 @@
         <v>90</v>
       </c>
       <c r="I46" s="0" t="s">
-        <v>285</v>
+        <v>603</v>
       </c>
       <c r="J46" s="0">
         <v>235.43600000000001</v>
@@ -3918,7 +3918,7 @@
         <v>91</v>
       </c>
       <c r="I47" s="0" t="s">
-        <v>286</v>
+        <v>604</v>
       </c>
       <c r="J47" s="0">
         <v>200.92150000000001</v>
@@ -3950,7 +3950,7 @@
         <v>92</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>287</v>
+        <v>605</v>
       </c>
       <c r="J48" s="0">
         <v>9411.1659999999993</v>
@@ -3982,7 +3982,7 @@
         <v>93</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>288</v>
+        <v>606</v>
       </c>
       <c r="J49" s="0">
         <v>9342.8192999999992</v>
@@ -4014,7 +4014,7 @@
         <v>94</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>289</v>
+        <v>607</v>
       </c>
       <c r="J50" s="0">
         <v>941.59280000000001</v>
@@ -4046,7 +4046,7 @@
         <v>95</v>
       </c>
       <c r="I51" s="0" t="s">
-        <v>290</v>
+        <v>608</v>
       </c>
       <c r="J51" s="0">
         <v>927.30880000000002</v>
@@ -4078,7 +4078,7 @@
         <v>96</v>
       </c>
       <c r="I52" s="0" t="s">
-        <v>291</v>
+        <v>609</v>
       </c>
       <c r="J52" s="0">
         <v>385.38529999999997</v>
@@ -4110,7 +4110,7 @@
         <v>97</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>292</v>
+        <v>610</v>
       </c>
       <c r="J53" s="0">
         <v>329.19709999999998</v>
@@ -4142,7 +4142,7 @@
         <v>98</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>293</v>
+        <v>611</v>
       </c>
       <c r="J54" s="0">
         <v>234.09270000000001</v>
@@ -4174,7 +4174,7 @@
         <v>99</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>294</v>
+        <v>612</v>
       </c>
       <c r="J55" s="0">
         <v>208.97069999999999</v>
@@ -4206,7 +4206,7 @@
         <v>100</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>295</v>
+        <v>613</v>
       </c>
       <c r="J56" s="0">
         <v>306.70839999999998</v>
@@ -4238,7 +4238,7 @@
         <v>101</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>296</v>
+        <v>614</v>
       </c>
       <c r="J57" s="0">
         <v>296.32659999999999</v>
@@ -4270,7 +4270,7 @@
         <v>102</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>297</v>
+        <v>615</v>
       </c>
       <c r="J58" s="0">
         <v>294.18619999999999</v>
@@ -4302,7 +4302,7 @@
         <v>103</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>298</v>
+        <v>616</v>
       </c>
       <c r="J59" s="0">
         <v>293.80200000000002</v>
@@ -4334,7 +4334,7 @@
         <v>104</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>299</v>
+        <v>617</v>
       </c>
       <c r="J60" s="0">
         <v>15461.819299999999</v>
@@ -4366,7 +4366,7 @@
         <v>105</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>300</v>
+        <v>618</v>
       </c>
       <c r="J61" s="0">
         <v>10367.752</v>
@@ -4398,7 +4398,7 @@
         <v>106</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>301</v>
+        <v>619</v>
       </c>
       <c r="J62" s="0">
         <v>1905.2927</v>
@@ -4430,7 +4430,7 @@
         <v>107</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>302</v>
+        <v>620</v>
       </c>
       <c r="J63" s="0">
         <v>975.92460000000005</v>
@@ -4462,7 +4462,7 @@
         <v>108</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>303</v>
+        <v>621</v>
       </c>
       <c r="J64" s="0">
         <v>581.38819999999998</v>
@@ -4494,7 +4494,7 @@
         <v>109</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>304</v>
+        <v>622</v>
       </c>
       <c r="J65" s="0">
         <v>546.27200000000005</v>
@@ -4526,7 +4526,7 @@
         <v>110</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>305</v>
+        <v>623</v>
       </c>
       <c r="J66" s="0">
         <v>536.43460000000005</v>
@@ -4558,7 +4558,7 @@
         <v>111</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>306</v>
+        <v>624</v>
       </c>
       <c r="J67" s="0">
         <v>533.26229999999998</v>
@@ -4590,7 +4590,7 @@
         <v>112</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>307</v>
+        <v>625</v>
       </c>
       <c r="J68" s="0">
         <v>523.20399999999995</v>
@@ -4622,7 +4622,7 @@
         <v>113</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>308</v>
+        <v>626</v>
       </c>
       <c r="J69" s="0">
         <v>516.61569999999995</v>
@@ -4654,7 +4654,7 @@
         <v>114</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>309</v>
+        <v>627</v>
       </c>
       <c r="J70" s="0">
         <v>479.05590000000001</v>
@@ -4686,7 +4686,7 @@
         <v>115</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>310</v>
+        <v>628</v>
       </c>
       <c r="J71" s="0">
         <v>442.88510000000002</v>
@@ -4718,7 +4718,7 @@
         <v>116</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>311</v>
+        <v>629</v>
       </c>
       <c r="J72" s="0">
         <v>384.4887</v>
@@ -4750,7 +4750,7 @@
         <v>117</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>312</v>
+        <v>630</v>
       </c>
       <c r="J73" s="0">
         <v>341.47399999999999</v>
@@ -4782,7 +4782,7 @@
         <v>118</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>313</v>
+        <v>631</v>
       </c>
       <c r="J74" s="0">
         <v>292.89060000000001</v>
@@ -4814,7 +4814,7 @@
         <v>119</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>314</v>
+        <v>632</v>
       </c>
       <c r="J75" s="0">
         <v>292.57459999999998</v>
@@ -4846,7 +4846,7 @@
         <v>120</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>315</v>
+        <v>633</v>
       </c>
       <c r="J76" s="0">
         <v>284.52800000000002</v>
@@ -4878,7 +4878,7 @@
         <v>61</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>316</v>
+        <v>634</v>
       </c>
       <c r="J77" s="0">
         <v>284.25450000000001</v>
@@ -4910,7 +4910,7 @@
         <v>121</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>317</v>
+        <v>635</v>
       </c>
       <c r="J78" s="0">
         <v>279.87459999999999</v>
@@ -4942,7 +4942,7 @@
         <v>122</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>318</v>
+        <v>636</v>
       </c>
       <c r="J79" s="0">
         <v>268.24270000000001</v>
@@ -4974,7 +4974,7 @@
         <v>443</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>529</v>
+        <v>637</v>
       </c>
       <c r="J80" s="0">
         <v>10499.483399999999</v>
@@ -5006,7 +5006,7 @@
         <v>444</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>530</v>
+        <v>638</v>
       </c>
       <c r="J81" s="0">
         <v>9639.3300999999992</v>
@@ -5038,7 +5038,7 @@
         <v>447</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>533</v>
+        <v>639</v>
       </c>
       <c r="J82" s="0">
         <v>388.74549999999999</v>
@@ -5070,7 +5070,7 @@
         <v>448</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>534</v>
+        <v>640</v>
       </c>
       <c r="J83" s="0">
         <v>308.16899999999998</v>
@@ -5102,7 +5102,7 @@
         <v>449</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>535</v>
+        <v>641</v>
       </c>
       <c r="J84" s="0">
         <v>305.76100000000002</v>
@@ -5134,7 +5134,7 @@
         <v>451</v>
       </c>
       <c r="I85" s="0" t="s">
-        <v>537</v>
+        <v>642</v>
       </c>
       <c r="J85" s="0">
         <v>297.43759999999998</v>
@@ -5166,7 +5166,7 @@
         <v>452</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>538</v>
+        <v>643</v>
       </c>
       <c r="J86" s="0">
         <v>283.1619</v>
@@ -5198,7 +5198,7 @@
         <v>453</v>
       </c>
       <c r="I87" s="0" t="s">
-        <v>539</v>
+        <v>644</v>
       </c>
       <c r="J87" s="0">
         <v>247.529</v>
@@ -5230,7 +5230,7 @@
         <v>454</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>540</v>
+        <v>645</v>
       </c>
       <c r="J88" s="0">
         <v>231.5712</v>
@@ -5262,7 +5262,7 @@
         <v>455</v>
       </c>
       <c r="I89" s="0" t="s">
-        <v>541</v>
+        <v>646</v>
       </c>
       <c r="J89" s="0">
         <v>1517.5046</v>
@@ -5294,7 +5294,7 @@
         <v>456</v>
       </c>
       <c r="I90" s="0" t="s">
-        <v>542</v>
+        <v>647</v>
       </c>
       <c r="J90" s="0">
         <v>1414.645</v>
@@ -5326,7 +5326,7 @@
         <v>457</v>
       </c>
       <c r="I91" s="0" t="s">
-        <v>543</v>
+        <v>648</v>
       </c>
       <c r="J91" s="0">
         <v>385.28089999999998</v>
@@ -5358,7 +5358,7 @@
         <v>458</v>
       </c>
       <c r="I92" s="0" t="s">
-        <v>544</v>
+        <v>649</v>
       </c>
       <c r="J92" s="0">
         <v>310.61110000000002</v>
@@ -5390,7 +5390,7 @@
         <v>459</v>
       </c>
       <c r="I93" s="0" t="s">
-        <v>545</v>
+        <v>650</v>
       </c>
       <c r="J93" s="0">
         <v>277.84199999999999</v>
@@ -5422,7 +5422,7 @@
         <v>63</v>
       </c>
       <c r="I94" s="0" t="s">
-        <v>546</v>
+        <v>651</v>
       </c>
       <c r="J94" s="0">
         <v>223.45169999999999</v>
@@ -5454,7 +5454,7 @@
         <v>460</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>547</v>
+        <v>652</v>
       </c>
       <c r="J95" s="0">
         <v>10215.762699999999</v>
@@ -5486,7 +5486,7 @@
         <v>461</v>
       </c>
       <c r="I96" s="0" t="s">
-        <v>548</v>
+        <v>653</v>
       </c>
       <c r="J96" s="0">
         <v>8851.0136999999995</v>
@@ -5518,7 +5518,7 @@
         <v>462</v>
       </c>
       <c r="I97" s="0" t="s">
-        <v>549</v>
+        <v>654</v>
       </c>
       <c r="J97" s="0">
         <v>1106.4232</v>
@@ -5550,7 +5550,7 @@
         <v>463</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>550</v>
+        <v>655</v>
       </c>
       <c r="J98" s="0">
         <v>909.94200000000001</v>
@@ -5582,7 +5582,7 @@
         <v>464</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>551</v>
+        <v>656</v>
       </c>
       <c r="J99" s="0">
         <v>316.77910000000003</v>
@@ -5614,7 +5614,7 @@
         <v>465</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>552</v>
+        <v>657</v>
       </c>
       <c r="J100" s="0">
         <v>284.43700000000001</v>
@@ -5646,7 +5646,7 @@
         <v>466</v>
       </c>
       <c r="I101" s="0" t="s">
-        <v>553</v>
+        <v>658</v>
       </c>
       <c r="J101" s="0">
         <v>282.07659999999999</v>
@@ -5678,7 +5678,7 @@
         <v>467</v>
       </c>
       <c r="I102" s="0" t="s">
-        <v>554</v>
+        <v>659</v>
       </c>
       <c r="J102" s="0">
         <v>261.52760000000001</v>
@@ -5710,7 +5710,7 @@
         <v>468</v>
       </c>
       <c r="I103" s="0" t="s">
-        <v>555</v>
+        <v>660</v>
       </c>
       <c r="J103" s="0">
         <v>248.01570000000001</v>
@@ -5742,7 +5742,7 @@
         <v>469</v>
       </c>
       <c r="I104" s="0" t="s">
-        <v>556</v>
+        <v>661</v>
       </c>
       <c r="J104" s="0">
         <v>246.53380000000001</v>
@@ -5774,7 +5774,7 @@
         <v>470</v>
       </c>
       <c r="I105" s="0" t="s">
-        <v>557</v>
+        <v>662</v>
       </c>
       <c r="J105" s="0">
         <v>228.9768</v>
@@ -5806,7 +5806,7 @@
         <v>471</v>
       </c>
       <c r="I106" s="0" t="s">
-        <v>558</v>
+        <v>663</v>
       </c>
       <c r="J106" s="0">
         <v>216.21680000000001</v>
@@ -5838,7 +5838,7 @@
         <v>123</v>
       </c>
       <c r="I107" s="0" t="s">
-        <v>319</v>
+        <v>664</v>
       </c>
       <c r="J107" s="0">
         <v>10261.8174</v>
@@ -5870,7 +5870,7 @@
         <v>124</v>
       </c>
       <c r="I108" s="0" t="s">
-        <v>320</v>
+        <v>665</v>
       </c>
       <c r="J108" s="0">
         <v>9826.5293000000001</v>
@@ -5902,7 +5902,7 @@
         <v>125</v>
       </c>
       <c r="I109" s="0" t="s">
-        <v>321</v>
+        <v>666</v>
       </c>
       <c r="J109" s="0">
         <v>310.85700000000003</v>
@@ -5934,7 +5934,7 @@
         <v>126</v>
       </c>
       <c r="I110" s="0" t="s">
-        <v>322</v>
+        <v>667</v>
       </c>
       <c r="J110" s="0">
         <v>294.82119999999998</v>
@@ -5966,7 +5966,7 @@
         <v>127</v>
       </c>
       <c r="I111" s="0" t="s">
-        <v>323</v>
+        <v>668</v>
       </c>
       <c r="J111" s="0">
         <v>290.76960000000003</v>
@@ -5998,7 +5998,7 @@
         <v>128</v>
       </c>
       <c r="I112" s="0" t="s">
-        <v>324</v>
+        <v>669</v>
       </c>
       <c r="J112" s="0">
         <v>273.49590000000001</v>
@@ -6030,7 +6030,7 @@
         <v>129</v>
       </c>
       <c r="I113" s="0" t="s">
-        <v>325</v>
+        <v>670</v>
       </c>
       <c r="J113" s="0">
         <v>242.22909999999999</v>
@@ -6062,7 +6062,7 @@
         <v>130</v>
       </c>
       <c r="I114" s="0" t="s">
-        <v>326</v>
+        <v>671</v>
       </c>
       <c r="J114" s="0">
         <v>238.70050000000001</v>
@@ -6094,7 +6094,7 @@
         <v>131</v>
       </c>
       <c r="I115" s="0" t="s">
-        <v>327</v>
+        <v>672</v>
       </c>
       <c r="J115" s="0">
         <v>227.2551</v>
@@ -6126,7 +6126,7 @@
         <v>132</v>
       </c>
       <c r="I116" s="0" t="s">
-        <v>328</v>
+        <v>673</v>
       </c>
       <c r="J116" s="0">
         <v>214.56540000000001</v>
@@ -6158,7 +6158,7 @@
         <v>133</v>
       </c>
       <c r="I117" s="0" t="s">
-        <v>329</v>
+        <v>674</v>
       </c>
       <c r="J117" s="0">
         <v>9905.6357000000007</v>
@@ -6190,7 +6190,7 @@
         <v>134</v>
       </c>
       <c r="I118" s="0" t="s">
-        <v>330</v>
+        <v>675</v>
       </c>
       <c r="J118" s="0">
         <v>8499.6309000000001</v>
@@ -6222,7 +6222,7 @@
         <v>135</v>
       </c>
       <c r="I119" s="0" t="s">
-        <v>331</v>
+        <v>676</v>
       </c>
       <c r="J119" s="0">
         <v>1404.5636</v>
@@ -6254,7 +6254,7 @@
         <v>136</v>
       </c>
       <c r="I120" s="0" t="s">
-        <v>332</v>
+        <v>677</v>
       </c>
       <c r="J120" s="0">
         <v>315.27960000000002</v>
@@ -6286,7 +6286,7 @@
         <v>137</v>
       </c>
       <c r="I121" s="0" t="s">
-        <v>333</v>
+        <v>678</v>
       </c>
       <c r="J121" s="0">
         <v>302.22129999999999</v>
@@ -6318,7 +6318,7 @@
         <v>138</v>
       </c>
       <c r="I122" s="0" t="s">
-        <v>334</v>
+        <v>679</v>
       </c>
       <c r="J122" s="0">
         <v>266.9862</v>
@@ -6350,7 +6350,7 @@
         <v>139</v>
       </c>
       <c r="I123" s="0" t="s">
-        <v>335</v>
+        <v>680</v>
       </c>
       <c r="J123" s="0">
         <v>264.11059999999998</v>
@@ -6382,7 +6382,7 @@
         <v>140</v>
       </c>
       <c r="I124" s="0" t="s">
-        <v>336</v>
+        <v>681</v>
       </c>
       <c r="J124" s="0">
         <v>247.79859999999999</v>
@@ -6414,7 +6414,7 @@
         <v>141</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>337</v>
+        <v>682</v>
       </c>
       <c r="J125" s="0">
         <v>239.36019999999999</v>
@@ -6446,7 +6446,7 @@
         <v>142</v>
       </c>
       <c r="I126" s="0" t="s">
-        <v>338</v>
+        <v>683</v>
       </c>
       <c r="J126" s="0">
         <v>208.72989999999999</v>
@@ -6478,7 +6478,7 @@
         <v>143</v>
       </c>
       <c r="I127" s="0" t="s">
-        <v>339</v>
+        <v>684</v>
       </c>
       <c r="J127" s="0">
         <v>199.44909999999999</v>
@@ -6510,7 +6510,7 @@
         <v>144</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>340</v>
+        <v>685</v>
       </c>
       <c r="J128" s="0">
         <v>9596.9883000000009</v>
@@ -6542,7 +6542,7 @@
         <v>145</v>
       </c>
       <c r="I129" s="0" t="s">
-        <v>341</v>
+        <v>686</v>
       </c>
       <c r="J129" s="0">
         <v>8798.1787000000004</v>
@@ -6574,7 +6574,7 @@
         <v>146</v>
       </c>
       <c r="I130" s="0" t="s">
-        <v>342</v>
+        <v>687</v>
       </c>
       <c r="J130" s="0">
         <v>1321.1365000000001</v>
@@ -6606,7 +6606,7 @@
         <v>147</v>
       </c>
       <c r="I131" s="0" t="s">
-        <v>343</v>
+        <v>688</v>
       </c>
       <c r="J131" s="0">
         <v>959.9144</v>
@@ -6638,7 +6638,7 @@
         <v>148</v>
       </c>
       <c r="I132" s="0" t="s">
-        <v>344</v>
+        <v>689</v>
       </c>
       <c r="J132" s="0">
         <v>309.23169999999999</v>
@@ -6670,7 +6670,7 @@
         <v>149</v>
       </c>
       <c r="I133" s="0" t="s">
-        <v>345</v>
+        <v>690</v>
       </c>
       <c r="J133" s="0">
         <v>301.12470000000002</v>
@@ -6702,7 +6702,7 @@
         <v>150</v>
       </c>
       <c r="I134" s="0" t="s">
-        <v>346</v>
+        <v>691</v>
       </c>
       <c r="J134" s="0">
         <v>296.84010000000001</v>
@@ -6734,7 +6734,7 @@
         <v>151</v>
       </c>
       <c r="I135" s="0" t="s">
-        <v>347</v>
+        <v>692</v>
       </c>
       <c r="J135" s="0">
         <v>288.2115</v>
@@ -6766,7 +6766,7 @@
         <v>152</v>
       </c>
       <c r="I136" s="0" t="s">
-        <v>348</v>
+        <v>693</v>
       </c>
       <c r="J136" s="0">
         <v>274.3639</v>
@@ -6798,7 +6798,7 @@
         <v>153</v>
       </c>
       <c r="I137" s="0" t="s">
-        <v>349</v>
+        <v>694</v>
       </c>
       <c r="J137" s="0">
         <v>260.00229999999999</v>
@@ -6830,7 +6830,7 @@
         <v>154</v>
       </c>
       <c r="I138" s="0" t="s">
-        <v>350</v>
+        <v>695</v>
       </c>
       <c r="J138" s="0">
         <v>246.21190000000001</v>
@@ -6862,7 +6862,7 @@
         <v>155</v>
       </c>
       <c r="I139" s="0" t="s">
-        <v>351</v>
+        <v>696</v>
       </c>
       <c r="J139" s="0">
         <v>180.47190000000001</v>
@@ -6894,7 +6894,7 @@
         <v>156</v>
       </c>
       <c r="I140" s="0" t="s">
-        <v>352</v>
+        <v>697</v>
       </c>
       <c r="J140" s="0">
         <v>9836.6807000000008</v>
@@ -6926,7 +6926,7 @@
         <v>158</v>
       </c>
       <c r="I141" s="0" t="s">
-        <v>354</v>
+        <v>698</v>
       </c>
       <c r="J141" s="0">
         <v>908.87840000000006</v>
@@ -6958,7 +6958,7 @@
         <v>159</v>
       </c>
       <c r="I142" s="0" t="s">
-        <v>355</v>
+        <v>699</v>
       </c>
       <c r="J142" s="0">
         <v>840.46699999999999</v>
@@ -6990,7 +6990,7 @@
         <v>160</v>
       </c>
       <c r="I143" s="0" t="s">
-        <v>356</v>
+        <v>700</v>
       </c>
       <c r="J143" s="0">
         <v>385.22919999999999</v>
@@ -7022,7 +7022,7 @@
         <v>161</v>
       </c>
       <c r="I144" s="0" t="s">
-        <v>357</v>
+        <v>701</v>
       </c>
       <c r="J144" s="0">
         <v>310.47890000000001</v>
@@ -7054,7 +7054,7 @@
         <v>162</v>
       </c>
       <c r="I145" s="0" t="s">
-        <v>358</v>
+        <v>702</v>
       </c>
       <c r="J145" s="0">
         <v>300.91699999999997</v>
@@ -7086,7 +7086,7 @@
         <v>163</v>
       </c>
       <c r="I146" s="0" t="s">
-        <v>359</v>
+        <v>703</v>
       </c>
       <c r="J146" s="0">
         <v>285.7113</v>
@@ -7118,7 +7118,7 @@
         <v>164</v>
       </c>
       <c r="I147" s="0" t="s">
-        <v>360</v>
+        <v>704</v>
       </c>
       <c r="J147" s="0">
         <v>255.1182</v>
@@ -7150,7 +7150,7 @@
         <v>165</v>
       </c>
       <c r="I148" s="0" t="s">
-        <v>361</v>
+        <v>705</v>
       </c>
       <c r="J148" s="0">
         <v>251.63229999999999</v>
@@ -7182,7 +7182,7 @@
         <v>166</v>
       </c>
       <c r="I149" s="0" t="s">
-        <v>362</v>
+        <v>706</v>
       </c>
       <c r="J149" s="0">
         <v>241.47989999999999</v>
@@ -7214,7 +7214,7 @@
         <v>167</v>
       </c>
       <c r="I150" s="0" t="s">
-        <v>363</v>
+        <v>707</v>
       </c>
       <c r="J150" s="0">
         <v>239.88820000000001</v>
@@ -7246,7 +7246,7 @@
         <v>168</v>
       </c>
       <c r="I151" s="0" t="s">
-        <v>364</v>
+        <v>708</v>
       </c>
       <c r="J151" s="0">
         <v>10661.891600000001</v>
@@ -7278,7 +7278,7 @@
         <v>169</v>
       </c>
       <c r="I152" s="0" t="s">
-        <v>365</v>
+        <v>709</v>
       </c>
       <c r="J152" s="0">
         <v>7643.7520000000004</v>
@@ -7310,7 +7310,7 @@
         <v>170</v>
       </c>
       <c r="I153" s="0" t="s">
-        <v>366</v>
+        <v>710</v>
       </c>
       <c r="J153" s="0">
         <v>1539.2754</v>
@@ -7342,7 +7342,7 @@
         <v>171</v>
       </c>
       <c r="I154" s="0" t="s">
-        <v>367</v>
+        <v>711</v>
       </c>
       <c r="J154" s="0">
         <v>1393.9193</v>
@@ -7374,7 +7374,7 @@
         <v>172</v>
       </c>
       <c r="I155" s="0" t="s">
-        <v>368</v>
+        <v>712</v>
       </c>
       <c r="J155" s="0">
         <v>457.66739999999999</v>
@@ -7406,7 +7406,7 @@
         <v>173</v>
       </c>
       <c r="I156" s="0" t="s">
-        <v>369</v>
+        <v>713</v>
       </c>
       <c r="J156" s="0">
         <v>419.16669999999999</v>
@@ -7438,7 +7438,7 @@
         <v>174</v>
       </c>
       <c r="I157" s="0" t="s">
-        <v>370</v>
+        <v>714</v>
       </c>
       <c r="J157" s="0">
         <v>417.49169999999998</v>
@@ -7470,7 +7470,7 @@
         <v>175</v>
       </c>
       <c r="I158" s="0" t="s">
-        <v>371</v>
+        <v>715</v>
       </c>
       <c r="J158" s="0">
         <v>399.00799999999998</v>
@@ -7502,7 +7502,7 @@
         <v>176</v>
       </c>
       <c r="I159" s="0" t="s">
-        <v>372</v>
+        <v>716</v>
       </c>
       <c r="J159" s="0">
         <v>361.1662</v>
@@ -7534,7 +7534,7 @@
         <v>178</v>
       </c>
       <c r="I160" s="0" t="s">
-        <v>374</v>
+        <v>717</v>
       </c>
       <c r="J160" s="0">
         <v>311.19600000000003</v>
@@ -7566,7 +7566,7 @@
         <v>179</v>
       </c>
       <c r="I161" s="0" t="s">
-        <v>375</v>
+        <v>718</v>
       </c>
       <c r="J161" s="0">
         <v>291.23480000000001</v>
@@ -7598,7 +7598,7 @@
         <v>180</v>
       </c>
       <c r="I162" s="0" t="s">
-        <v>376</v>
+        <v>719</v>
       </c>
       <c r="J162" s="0">
         <v>9127.5985999999994</v>
@@ -7630,7 +7630,7 @@
         <v>181</v>
       </c>
       <c r="I163" s="0" t="s">
-        <v>377</v>
+        <v>720</v>
       </c>
       <c r="J163" s="0">
         <v>8554.8642999999993</v>
@@ -7662,7 +7662,7 @@
         <v>182</v>
       </c>
       <c r="I164" s="0" t="s">
-        <v>378</v>
+        <v>721</v>
       </c>
       <c r="J164" s="0">
         <v>1414.848</v>
@@ -7694,7 +7694,7 @@
         <v>183</v>
       </c>
       <c r="I165" s="0" t="s">
-        <v>379</v>
+        <v>722</v>
       </c>
       <c r="J165" s="0">
         <v>752.67660000000001</v>
@@ -7726,7 +7726,7 @@
         <v>184</v>
       </c>
       <c r="I166" s="0" t="s">
-        <v>380</v>
+        <v>723</v>
       </c>
       <c r="J166" s="0">
         <v>348.73090000000002</v>
@@ -7758,7 +7758,7 @@
         <v>185</v>
       </c>
       <c r="I167" s="0" t="s">
-        <v>381</v>
+        <v>724</v>
       </c>
       <c r="J167" s="0">
         <v>307.04939999999999</v>
@@ -7790,7 +7790,7 @@
         <v>186</v>
       </c>
       <c r="I168" s="0" t="s">
-        <v>382</v>
+        <v>725</v>
       </c>
       <c r="J168" s="0">
         <v>280.97919999999999</v>
@@ -7822,7 +7822,7 @@
         <v>187</v>
       </c>
       <c r="I169" s="0" t="s">
-        <v>383</v>
+        <v>726</v>
       </c>
       <c r="J169" s="0">
         <v>265.1284</v>
@@ -7854,7 +7854,7 @@
         <v>188</v>
       </c>
       <c r="I170" s="0" t="s">
-        <v>384</v>
+        <v>727</v>
       </c>
       <c r="J170" s="0">
         <v>249.8895</v>
@@ -7886,7 +7886,7 @@
         <v>189</v>
       </c>
       <c r="I171" s="0" t="s">
-        <v>385</v>
+        <v>728</v>
       </c>
       <c r="J171" s="0">
         <v>215.3955</v>
@@ -7918,7 +7918,7 @@
         <v>190</v>
       </c>
       <c r="I172" s="0" t="s">
-        <v>386</v>
+        <v>729</v>
       </c>
       <c r="J172" s="0">
         <v>213.6302</v>
@@ -7950,7 +7950,7 @@
         <v>191</v>
       </c>
       <c r="I173" s="0" t="s">
-        <v>387</v>
+        <v>730</v>
       </c>
       <c r="J173" s="0">
         <v>193.54920000000001</v>
@@ -7982,7 +7982,7 @@
         <v>192</v>
       </c>
       <c r="I174" s="0" t="s">
-        <v>388</v>
+        <v>731</v>
       </c>
       <c r="J174" s="0">
         <v>9254.9814000000006</v>
@@ -8014,7 +8014,7 @@
         <v>193</v>
       </c>
       <c r="I175" s="0" t="s">
-        <v>389</v>
+        <v>732</v>
       </c>
       <c r="J175" s="0">
         <v>8396.3974999999991</v>
@@ -8046,7 +8046,7 @@
         <v>194</v>
       </c>
       <c r="I176" s="0" t="s">
-        <v>390</v>
+        <v>733</v>
       </c>
       <c r="J176" s="0">
         <v>1087.1931999999999</v>
@@ -8078,7 +8078,7 @@
         <v>195</v>
       </c>
       <c r="I177" s="0" t="s">
-        <v>391</v>
+        <v>734</v>
       </c>
       <c r="J177" s="0">
         <v>1026.0048999999999</v>
@@ -8110,7 +8110,7 @@
         <v>196</v>
       </c>
       <c r="I178" s="0" t="s">
-        <v>392</v>
+        <v>735</v>
       </c>
       <c r="J178" s="0">
         <v>328.2697</v>
@@ -8142,7 +8142,7 @@
         <v>197</v>
       </c>
       <c r="I179" s="0" t="s">
-        <v>393</v>
+        <v>736</v>
       </c>
       <c r="J179" s="0">
         <v>306.13749999999999</v>
@@ -8174,7 +8174,7 @@
         <v>198</v>
       </c>
       <c r="I180" s="0" t="s">
-        <v>394</v>
+        <v>737</v>
       </c>
       <c r="J180" s="0">
         <v>302.69369999999998</v>
@@ -8206,7 +8206,7 @@
         <v>199</v>
       </c>
       <c r="I181" s="0" t="s">
-        <v>395</v>
+        <v>738</v>
       </c>
       <c r="J181" s="0">
         <v>296.63529999999997</v>
@@ -8238,7 +8238,7 @@
         <v>200</v>
       </c>
       <c r="I182" s="0" t="s">
-        <v>396</v>
+        <v>739</v>
       </c>
       <c r="J182" s="0">
         <v>292.96969999999999</v>
@@ -8270,7 +8270,7 @@
         <v>201</v>
       </c>
       <c r="I183" s="0" t="s">
-        <v>397</v>
+        <v>740</v>
       </c>
       <c r="J183" s="0">
         <v>267.35629999999998</v>
@@ -8302,7 +8302,7 @@
         <v>203</v>
       </c>
       <c r="I184" s="0" t="s">
-        <v>399</v>
+        <v>741</v>
       </c>
       <c r="J184" s="0">
         <v>165.21969999999999</v>
@@ -8334,7 +8334,7 @@
         <v>206</v>
       </c>
       <c r="I185" s="0" t="s">
-        <v>402</v>
+        <v>742</v>
       </c>
       <c r="J185" s="0">
         <v>1713.3430000000001</v>
@@ -8366,7 +8366,7 @@
         <v>207</v>
       </c>
       <c r="I186" s="0" t="s">
-        <v>403</v>
+        <v>743</v>
       </c>
       <c r="J186" s="0">
         <v>1254.9603</v>
@@ -8398,7 +8398,7 @@
         <v>208</v>
       </c>
       <c r="I187" s="0" t="s">
-        <v>404</v>
+        <v>744</v>
       </c>
       <c r="J187" s="0">
         <v>412.1336</v>
@@ -8430,7 +8430,7 @@
         <v>209</v>
       </c>
       <c r="I188" s="0" t="s">
-        <v>405</v>
+        <v>745</v>
       </c>
       <c r="J188" s="0">
         <v>395.3304</v>
@@ -8462,7 +8462,7 @@
         <v>210</v>
       </c>
       <c r="I189" s="0" t="s">
-        <v>406</v>
+        <v>746</v>
       </c>
       <c r="J189" s="0">
         <v>314.40159999999997</v>
@@ -8494,7 +8494,7 @@
         <v>211</v>
       </c>
       <c r="I190" s="0" t="s">
-        <v>407</v>
+        <v>747</v>
       </c>
       <c r="J190" s="0">
         <v>306.70960000000002</v>
@@ -8526,7 +8526,7 @@
         <v>212</v>
       </c>
       <c r="I191" s="0" t="s">
-        <v>408</v>
+        <v>748</v>
       </c>
       <c r="J191" s="0">
         <v>285.86070000000001</v>
@@ -8558,7 +8558,7 @@
         <v>213</v>
       </c>
       <c r="I192" s="0" t="s">
-        <v>409</v>
+        <v>749</v>
       </c>
       <c r="J192" s="0">
         <v>284.4486</v>
@@ -8590,7 +8590,7 @@
         <v>214</v>
       </c>
       <c r="I193" s="0" t="s">
-        <v>410</v>
+        <v>750</v>
       </c>
       <c r="J193" s="0">
         <v>281.97449999999998</v>
@@ -8622,7 +8622,7 @@
         <v>216</v>
       </c>
       <c r="I194" s="0" t="s">
-        <v>412</v>
+        <v>751</v>
       </c>
       <c r="J194" s="0">
         <v>9423.6895000000004</v>
@@ -8654,7 +8654,7 @@
         <v>217</v>
       </c>
       <c r="I195" s="0" t="s">
-        <v>413</v>
+        <v>752</v>
       </c>
       <c r="J195" s="0">
         <v>9234.3525000000009</v>
@@ -8686,7 +8686,7 @@
         <v>218</v>
       </c>
       <c r="I196" s="0" t="s">
-        <v>414</v>
+        <v>753</v>
       </c>
       <c r="J196" s="0">
         <v>1208.9946</v>
@@ -8718,7 +8718,7 @@
         <v>219</v>
       </c>
       <c r="I197" s="0" t="s">
-        <v>415</v>
+        <v>754</v>
       </c>
       <c r="J197" s="0">
         <v>951.19749999999999</v>
@@ -8750,7 +8750,7 @@
         <v>220</v>
       </c>
       <c r="I198" s="0" t="s">
-        <v>416</v>
+        <v>755</v>
       </c>
       <c r="J198" s="0">
         <v>316.12619999999998</v>
@@ -8782,7 +8782,7 @@
         <v>221</v>
       </c>
       <c r="I199" s="0" t="s">
-        <v>417</v>
+        <v>756</v>
       </c>
       <c r="J199" s="0">
         <v>302.2124</v>
@@ -8814,7 +8814,7 @@
         <v>222</v>
       </c>
       <c r="I200" s="0" t="s">
-        <v>418</v>
+        <v>757</v>
       </c>
       <c r="J200" s="0">
         <v>294.96859999999998</v>
@@ -8846,7 +8846,7 @@
         <v>223</v>
       </c>
       <c r="I201" s="0" t="s">
-        <v>419</v>
+        <v>758</v>
       </c>
       <c r="J201" s="0">
         <v>291.27109999999999</v>
@@ -8878,7 +8878,7 @@
         <v>224</v>
       </c>
       <c r="I202" s="0" t="s">
-        <v>420</v>
+        <v>759</v>
       </c>
       <c r="J202" s="0">
         <v>264.68939999999998</v>
@@ -8910,7 +8910,7 @@
         <v>225</v>
       </c>
       <c r="I203" s="0" t="s">
-        <v>421</v>
+        <v>760</v>
       </c>
       <c r="J203" s="0">
         <v>257.6934</v>
@@ -8942,7 +8942,7 @@
         <v>226</v>
       </c>
       <c r="I204" s="0" t="s">
-        <v>422</v>
+        <v>761</v>
       </c>
       <c r="J204" s="0">
         <v>214.37610000000001</v>
@@ -8974,7 +8974,7 @@
         <v>227</v>
       </c>
       <c r="I205" s="0" t="s">
-        <v>423</v>
+        <v>762</v>
       </c>
       <c r="J205" s="0">
         <v>190.58150000000001</v>
@@ -9006,7 +9006,7 @@
         <v>228</v>
       </c>
       <c r="I206" s="0" t="s">
-        <v>424</v>
+        <v>763</v>
       </c>
       <c r="J206" s="0">
         <v>10441.448200000001</v>
@@ -9038,7 +9038,7 @@
         <v>229</v>
       </c>
       <c r="I207" s="0" t="s">
-        <v>425</v>
+        <v>764</v>
       </c>
       <c r="J207" s="0">
         <v>9728.8516</v>
@@ -9070,7 +9070,7 @@
         <v>230</v>
       </c>
       <c r="I208" s="0" t="s">
-        <v>426</v>
+        <v>765</v>
       </c>
       <c r="J208" s="0">
         <v>1533.4409000000001</v>
@@ -9102,7 +9102,7 @@
         <v>231</v>
       </c>
       <c r="I209" s="0" t="s">
-        <v>427</v>
+        <v>766</v>
       </c>
       <c r="J209" s="0">
         <v>1358.2428</v>
@@ -9134,7 +9134,7 @@
         <v>232</v>
       </c>
       <c r="I210" s="0" t="s">
-        <v>428</v>
+        <v>767</v>
       </c>
       <c r="J210" s="0">
         <v>452.1069</v>
@@ -9166,7 +9166,7 @@
         <v>233</v>
       </c>
       <c r="I211" s="0" t="s">
-        <v>429</v>
+        <v>768</v>
       </c>
       <c r="J211" s="0">
         <v>439.75790000000001</v>
@@ -9198,7 +9198,7 @@
         <v>234</v>
       </c>
       <c r="I212" s="0" t="s">
-        <v>430</v>
+        <v>769</v>
       </c>
       <c r="J212" s="0">
         <v>376.52229999999997</v>
@@ -9230,7 +9230,7 @@
         <v>235</v>
       </c>
       <c r="I213" s="0" t="s">
-        <v>431</v>
+        <v>770</v>
       </c>
       <c r="J213" s="0">
         <v>375.43979999999999</v>
@@ -9262,7 +9262,7 @@
         <v>236</v>
       </c>
       <c r="I214" s="0" t="s">
-        <v>432</v>
+        <v>771</v>
       </c>
       <c r="J214" s="0">
         <v>373.55439999999999</v>
@@ -9294,7 +9294,7 @@
         <v>237</v>
       </c>
       <c r="I215" s="0" t="s">
-        <v>433</v>
+        <v>772</v>
       </c>
       <c r="J215" s="0">
         <v>302.76659999999998</v>
@@ -9326,7 +9326,7 @@
         <v>238</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>434</v>
+        <v>773</v>
       </c>
       <c r="J216" s="0">
         <v>300.86579999999998</v>
@@ -9358,7 +9358,7 @@
         <v>472</v>
       </c>
       <c r="I217" s="0" t="s">
-        <v>514</v>
+        <v>774</v>
       </c>
       <c r="J217" s="0">
         <v>12892.7021</v>
@@ -9390,7 +9390,7 @@
         <v>473</v>
       </c>
       <c r="I218" s="0" t="s">
-        <v>515</v>
+        <v>775</v>
       </c>
       <c r="J218" s="0">
         <v>10694.238300000001</v>
@@ -9422,7 +9422,7 @@
         <v>474</v>
       </c>
       <c r="I219" s="0" t="s">
-        <v>516</v>
+        <v>776</v>
       </c>
       <c r="J219" s="0">
         <v>2047.9614999999999</v>
@@ -9454,7 +9454,7 @@
         <v>475</v>
       </c>
       <c r="I220" s="0" t="s">
-        <v>517</v>
+        <v>777</v>
       </c>
       <c r="J220" s="0">
         <v>910.678</v>
@@ -9486,7 +9486,7 @@
         <v>477</v>
       </c>
       <c r="I221" s="0" t="s">
-        <v>519</v>
+        <v>778</v>
       </c>
       <c r="J221" s="0">
         <v>568.2056</v>
@@ -9518,7 +9518,7 @@
         <v>479</v>
       </c>
       <c r="I222" s="0" t="s">
-        <v>521</v>
+        <v>779</v>
       </c>
       <c r="J222" s="0">
         <v>489.4178</v>
@@ -9550,7 +9550,7 @@
         <v>481</v>
       </c>
       <c r="I223" s="0" t="s">
-        <v>523</v>
+        <v>780</v>
       </c>
       <c r="J223" s="0">
         <v>370.15899999999999</v>
@@ -9582,7 +9582,7 @@
         <v>483</v>
       </c>
       <c r="I224" s="0" t="s">
-        <v>525</v>
+        <v>781</v>
       </c>
       <c r="J224" s="0">
         <v>340.95030000000003</v>
